--- a/output/full_scan/batch_seq1_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1455</v>
+        <v>1303</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>853.8000379800419</v>
+        <v>1124.666986441613</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.2</v>
+        <v>139</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>73.07598197206623</v>
+        <v>75.52295598053001</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43.02226709437036</v>
+        <v>27.24211949174877</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.197635395191481</v>
+        <v>1.585293264694812</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.06713955008462399</v>
+        <v>3.111713921484736</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>814.6669864416126</v>
+        <v>1046.255618502927</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>139</v>
+        <v>51.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>75.52295598053001</v>
+        <v>62.21016802523258</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.24211949174876</v>
+        <v>19.16335923757461</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.585293264694812</v>
+        <v>4.725561850292678</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3.111713921475182</v>
+        <v>0.3740003764816376</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1503</v>
+        <v>1326</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>752.7061157387524</v>
+        <v>934.43296239753</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>241.5</v>
+        <v>54.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.61356524461225</v>
+        <v>61.51001365471994</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21.4247710647293</v>
+        <v>22.00852447016627</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.8997420603596417</v>
+        <v>0.8427534813529766</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0577965946305853</v>
+        <v>0.3867066854077279</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1436</v>
+        <v>1503</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>748.7050098124354</v>
+        <v>892.7061157387524</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>47.5</v>
+        <v>241.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>55.52348302553762</v>
+        <v>61.61356524461225</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.59806962587242</v>
+        <v>21.42477104101332</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.682746045526478</v>
+        <v>0.8997420603596417</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4113201449873369</v>
+        <v>0.0577965948213785</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1563</v>
+        <v>1455</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>745.6222295637924</v>
+        <v>863.8000379800418</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67.7</v>
+        <v>10.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.13214971870855</v>
+        <v>73.07598197540156</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45.13927427820936</v>
+        <v>43.02226714854736</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.274472021495549</v>
+        <v>2.197635395191481</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3015448541616594</v>
+        <v>0.0671395500903484</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>739.5497812820505</v>
+        <v>854.5497812820505</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>54.7</v>
@@ -817,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.00850907350483</v>
+        <v>56.00850916201571</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>28.29750800717133</v>
@@ -826,40 +826,40 @@
         <v>0.5941407308952612</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1376317583402213</v>
+        <v>0.1376317583020645</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1307</v>
+        <v>1342</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>727.2601313372636</v>
+        <v>815.7538899352642</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>36.4</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.82540955242763</v>
+        <v>72.52214129145692</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30.89402954834913</v>
+        <v>41.98778044201702</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5260131337263608</v>
+        <v>0.9947541827124956</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2988626557255907</v>
+        <v>1.485242999900608</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1432</v>
+        <v>1513</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>725.0816647553238</v>
+        <v>803.4700676590958</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17.6</v>
+        <v>176.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.14435190264871</v>
+        <v>61.67521166497431</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.35439012283427</v>
+        <v>21.14224504369142</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.153957115632234</v>
+        <v>0.8880220477980655</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0650262759766745</v>
+        <v>-0.1196359775771456</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>716.2556185029268</v>
+        <v>802.2601313372636</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>51.7</v>
+        <v>36.4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.21016803827122</v>
+        <v>68.82540943480555</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.16335923757461</v>
+        <v>30.89402956076432</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.725561850292678</v>
+        <v>0.5260131337263608</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3740003764720968</v>
+        <v>0.2988626560117808</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1568</v>
+        <v>1236</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>716.0272276098457</v>
+        <v>797.8456021055274</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46.05</v>
+        <v>25.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.93780717336179</v>
+        <v>63.21876149397025</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45.83260834642915</v>
+        <v>14.97363160233272</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.229706187786221</v>
+        <v>3.05312651146466</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.236556762198707</v>
+        <v>0.1159850736446855</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1236</v>
+        <v>1436</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>687.8456021055274</v>
+        <v>748.7050098124354</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>25.8</v>
+        <v>47.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>63.21877001415277</v>
+        <v>55.5234829461923</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14.97363160922288</v>
+        <v>29.5980696850501</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.05312651146466</v>
+        <v>1.682746045526478</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1159850736160673</v>
+        <v>0.4113201450827294</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1342</v>
+        <v>1304</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>680.7538899352642</v>
+        <v>736.3122637934827</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>116</v>
+        <v>13.55</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>72.52214131862911</v>
+        <v>56.82189578120946</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>41.9877804252247</v>
+        <v>17.43802983977482</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9947541827124956</v>
+        <v>1.36337126941053</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.485242999900608</v>
+        <v>0.08904455322678299</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>678.3656810588507</v>
+        <v>726.242673475292</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>32.15</v>
+        <v>43.95</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>68.33980310003858</v>
+        <v>55.03984517232819</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>44.50987233398091</v>
+        <v>25.37716800699772</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.440236062360517</v>
+        <v>0.7716085142239336</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3848319476717015</v>
+        <v>-0.0266077430382258</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1533</v>
+        <v>1432</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>674.5110239426173</v>
+        <v>725.0816647553238</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>38.2</v>
+        <v>17.6</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>54.66709620701491</v>
+        <v>66.1443518782105</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>49.05853770852155</v>
+        <v>22.35439014996757</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3306317089805499</v>
+        <v>2.153957115632234</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.3217233625296525</v>
+        <v>0.06502627600529511</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1444</v>
+        <v>1456</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>657.5542567724973</v>
+        <v>723.5060746387871</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.04</v>
+        <v>15.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.84261112422931</v>
+        <v>71.73396626291438</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33.48109326771503</v>
+        <v>21.70634066446499</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4787007153984733</v>
+        <v>1.45060746387871</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0153050651000305</v>
+        <v>0.2194367130684937</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1326</v>
+        <v>1525</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>654.4318149771099</v>
+        <v>701.5406374380354</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>54.2</v>
+        <v>66</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.51001367216705</v>
+        <v>51.98658037841993</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.00852447016627</v>
+        <v>27.27099740091602</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8426760281017605</v>
+        <v>0.2254912162044985</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3867066853695619</v>
+        <v>-0.4187585458299818</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>649.6088013199532</v>
+        <v>699.5396528141365</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99.2</v>
+        <v>11.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.42020482925876</v>
+        <v>59.40777970188018</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.27035653792626</v>
+        <v>19.53659650926148</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.252047492523111</v>
+        <v>1.047899710641487</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0985646836519373</v>
+        <v>0.07192872993325421</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1216</v>
+        <v>1515</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>647.1691844633698</v>
+        <v>699.3100456859476</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>74.5</v>
+        <v>25.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53.14904449407288</v>
+        <v>64.43587110969604</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.76337918436672</v>
+        <v>23.7993265557867</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.503011962191523</v>
+        <v>2.031004568594761</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.149866931789563</v>
+        <v>0.2364530078577263</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1419</v>
+        <v>1434</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>640.7799540690779</v>
+        <v>692.8838996269352</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>16.95</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>57.42886701945496</v>
+        <v>65.99272823920637</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.54105186673982</v>
+        <v>25.92622368880813</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4701577426923286</v>
+        <v>0.920412451593225</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.117014034272866</v>
+        <v>0.1077369110086075</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1409</v>
+        <v>1338</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>639.8202770200872</v>
+        <v>686.0157226220391</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>25.6</v>
+        <v>17.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.86688740310615</v>
+        <v>60.37026794230912</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>33.90228868936116</v>
+        <v>21.52508560192718</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.645819034232483</v>
+        <v>0.2960259134605936</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.069167682684923</v>
+        <v>0.0667006189894196</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1532</v>
+        <v>1321</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>624.8475551936692</v>
+        <v>678.3656810588507</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>24</v>
+        <v>32.15</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>72.49973663597416</v>
+        <v>68.33980308725089</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>40.63110814792856</v>
+        <v>44.5098725515812</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.179435935390436</v>
+        <v>1.440236062360517</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2323397003944711</v>
+        <v>0.3848319477861786</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1475</v>
+        <v>1402</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>618.7254215845576</v>
+        <v>676.5070199521294</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>27.4</v>
+        <v>28.85</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.00758691483706</v>
+        <v>63.03970351754613</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.6007751814056</v>
+        <v>18.29242953046834</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.992961267887884</v>
+        <v>0.5014713294127671</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2629530788573574</v>
+        <v>0.2309345337692722</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1513</v>
+        <v>1319</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>613.4700676590958</v>
+        <v>659.6088013199532</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>176.5</v>
+        <v>99.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.6752116203137</v>
+        <v>57.42020484759104</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.14224504261474</v>
+        <v>36.27035655853308</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8880220477980655</v>
+        <v>1.252047492523111</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.1196359773863409</v>
+        <v>0.09856468346116461</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1227</v>
+        <v>1444</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>612.2643517411922</v>
+        <v>657.5542567724973</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>29.1</v>
+        <v>7.04</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.73017833781979</v>
+        <v>58.84261111634376</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>18.76801256717508</v>
+        <v>33.4810933077659</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9092581356694578</v>
+        <v>0.4787007153984733</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1147458914895755</v>
+        <v>0.0153050651076618</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1525</v>
+        <v>1102</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>591.5406374380354</v>
+        <v>652.8802183208379</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>66</v>
+        <v>35.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.98658036788998</v>
+        <v>63.25795357631394</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.27099743304359</v>
+        <v>16.24054038084162</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2254912162044985</v>
+        <v>0.7292745764137463</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.4187585459253834</v>
+        <v>0.2460159324520993</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1446</v>
+        <v>1310</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>585.9669472862163</v>
+        <v>649.2035235197391</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>16.7</v>
+        <v>9.26</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>60.10552187832769</v>
+        <v>60.10062592635524</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>26.7509635462567</v>
+        <v>20.17743653583982</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7044634451767535</v>
+        <v>2.376397343442056</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0408561488792894</v>
+        <v>0.0876633298989556</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1104</v>
+        <v>1216</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>584.5331908379574</v>
+        <v>647.4525091711652</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.1</v>
+        <v>74.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.09469354603132</v>
+        <v>53.14904454895826</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.08434180216961</v>
+        <v>20.76337920467265</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.673098637683775</v>
+        <v>1.569797742192853</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.07719596890004531</v>
+        <v>0.1498669317323347</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1456</v>
+        <v>1419</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>583.5060746387871</v>
+        <v>640.7799540690776</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>71.73396630326937</v>
+        <v>57.42886703956965</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.70634063722932</v>
+        <v>21.54105185696687</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.45060746387871</v>
+        <v>0.4701577426923286</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2194367130398749</v>
+        <v>0.117014034272866</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1434</v>
+        <v>1409</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>582.8838996269351</v>
+        <v>624.8202770200872</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16.95</v>
+        <v>25.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>65.99272824851455</v>
+        <v>58.86688740500579</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.92622369979021</v>
+        <v>33.90228862072883</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.920412451593225</v>
+        <v>1.645819034232483</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1077369109990718</v>
+        <v>-0.0691676826753822</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>579.5396528141365</v>
+        <v>620.3260340202017</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11.6</v>
+        <v>13.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.4077796978506</v>
+        <v>58.90061377914206</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>19.53659653107001</v>
+        <v>30.0566255908111</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.047899710641487</v>
+        <v>0.5972918402774777</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0719287299218062</v>
+        <v>0.0500154251928375</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1102</v>
+        <v>1475</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>577.8802183208379</v>
+        <v>618.7254215845575</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>35.8</v>
+        <v>27.4</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.25795340521574</v>
+        <v>61.00758688017953</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.24054034181375</v>
+        <v>22.6007751814056</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7292745764137463</v>
+        <v>0.992961267887884</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2460159325474978</v>
+        <v>0.2629530789050555</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1338</v>
+        <v>1227</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>576.0157226220392</v>
+        <v>612.2643517411922</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>17.2</v>
+        <v>29.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.37026794230912</v>
+        <v>56.73017837542036</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.5250855405374</v>
+        <v>18.7680127063311</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2960259134605936</v>
+        <v>0.9092581356694578</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0667006189798808</v>
+        <v>0.1147458914991183</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1477</v>
+        <v>1225</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>561.5466910334385</v>
+        <v>609.5081289041721</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>221.5</v>
+        <v>32.25</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.31852118329154</v>
+        <v>59.15724440147043</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.21489129792619</v>
+        <v>21.48631186884588</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.652671112942963</v>
+        <v>0.7508128904172097</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.2581856525974541</v>
+        <v>0.4051218759914243</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1402</v>
+        <v>1446</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>561.0675160887007</v>
+        <v>605.9669472862163</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>28.85</v>
+        <v>16.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>63.03970352455892</v>
+        <v>60.10552185122149</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.29242950933858</v>
+        <v>26.75096354072749</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4721444193282408</v>
+        <v>0.7044634451767535</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2309345337024931</v>
+        <v>0.0408561489174495</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1314</v>
+        <v>1104</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>560.2895479050012</v>
+        <v>584.5331908379574</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7.78</v>
+        <v>29.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.2306908346671</v>
+        <v>62.09469360791442</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.09222660574242</v>
+        <v>31.08434188280217</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6112692406684329</v>
+        <v>1.673098637683775</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0040936721288783</v>
+        <v>0.077195968919125</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1560</v>
+        <v>1314</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>551.1803823826001</v>
+        <v>580.2895479050012</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>700</v>
+        <v>7.78</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.54323352750575</v>
+        <v>55.23069085151434</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.07441879874873</v>
+        <v>15.09222657468816</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5133909302682753</v>
+        <v>0.6112692406684329</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-4.647935624640869</v>
+        <v>0.0040936721384182</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1414</v>
+        <v>1101</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>549.824161959153</v>
+        <v>573.4302563936706</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.5</v>
+        <v>24.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>64.79735509461736</v>
+        <v>51.76456283138577</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.69874319060803</v>
+        <v>14.91001708951427</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3910277401585884</v>
+        <v>0.9638060972957572</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1932562637374036</v>
+        <v>0.0472354811198828</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1110</v>
+        <v>1477</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>547.9092829079706</v>
+        <v>571.5466910334386</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15.55</v>
+        <v>221.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.18459200030711</v>
+        <v>49.31852108141658</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.88317198925518</v>
+        <v>23.21489132688848</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6772333045779196</v>
+        <v>1.652671112942963</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0629090938061521</v>
+        <v>-0.2581856510711137</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1514</v>
+        <v>1308</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>547.0340572788257</v>
+        <v>559.6601571998519</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>121.5</v>
+        <v>13.95</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.95987326694552</v>
+        <v>53.64491994868592</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.3484494212368</v>
+        <v>14.73111346876891</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3473575093056278</v>
+        <v>1.131505124513402</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.30619983612317</v>
+        <v>0.0881924123875675</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1312</v>
+        <v>1414</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>544.6522158042316</v>
+        <v>549.8241619591524</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.90061378986501</v>
+        <v>64.79735522798596</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>30.05662556633614</v>
+        <v>25.69874319390791</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5507419545891211</v>
+        <v>0.3910277401585884</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0500154251642191</v>
+        <v>0.1932562636720068</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1339</v>
+        <v>1476</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>541.242673475292</v>
+        <v>549.0748523148882</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>43.95</v>
+        <v>327</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.03984522822914</v>
+        <v>40.66196375066807</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.37716802923265</v>
+        <v>13.78585032809397</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7716085142239336</v>
+        <v>1.427371551081816</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0266077432099397</v>
+        <v>-2.400246122748035</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1453</v>
+        <v>1110</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>531.988111470459</v>
+        <v>547.9092829079705</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11.8</v>
+        <v>15.55</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.93735085756109</v>
+        <v>57.18459198908</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.90554225387556</v>
+        <v>32.88317198925517</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4988111470458976</v>
+        <v>0.6772333045779196</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0778639642178912</v>
+        <v>0.0629090938443119</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>529.3100456859477</v>
+        <v>547.0340572788253</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>25.9</v>
+        <v>121.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>64.43587109383155</v>
+        <v>48.9598732746133</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.79932659109006</v>
+        <v>23.34844941935013</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.031004568594761</v>
+        <v>0.3473575093056278</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2364530078672667</v>
+        <v>-1.30619983612317</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1442</v>
+        <v>1465</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>523.9317216144626</v>
+        <v>540.8765755558298</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.30938288344236</v>
+        <v>57.66207980402617</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.40777418310417</v>
+        <v>14.39883835428248</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8837519370650183</v>
+        <v>0.4828718709459609</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1382591926066737</v>
+        <v>0.0102360332756602</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1504</v>
+        <v>1453</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>512.1720945122786</v>
+        <v>531.988111470459</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>70</v>
+        <v>11.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.16487608524703</v>
+        <v>56.93735087282981</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.95656552809883</v>
+        <v>27.90554225387556</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4153806981740384</v>
+        <v>0.4988111470458976</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.9550825538889304</v>
+        <v>0.07786396424651019</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1310</v>
+        <v>1442</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>509.203523519739</v>
+        <v>523.9317216144625</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9.26</v>
+        <v>28</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>60.10062591555505</v>
+        <v>57.30938267660233</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.17743657365481</v>
+        <v>21.4077746077942</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.376397343442056</v>
+        <v>0.8837519370650183</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.08766332989513791</v>
+        <v>0.138259192702071</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1423</v>
+        <v>1229</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>507.9161411936741</v>
+        <v>514.4295924979665</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>39.65</v>
+        <v>41.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.1379338541673</v>
+        <v>54.04519475643837</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>28.26850917064759</v>
+        <v>25.35375012840548</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3916141193674077</v>
+        <v>0.947929693493524</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2080426105167001</v>
+        <v>0.1214437077844433</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1474</v>
+        <v>1504</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>504.2037480061647</v>
+        <v>512.1720945122786</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10.25</v>
+        <v>70</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.2316414059153</v>
+        <v>47.16487611591501</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28.31508077889269</v>
+        <v>21.95656548367733</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4714339473541764</v>
+        <v>0.4153806981740384</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.004590398149669</v>
+        <v>-0.9550825539175456</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1304</v>
+        <v>1423</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>501.3122637934827</v>
+        <v>507.9161411936741</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>13.55</v>
+        <v>39.65</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>56.82189577434492</v>
+        <v>33.13793386110925</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.43802985749625</v>
+        <v>28.26850913452445</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.36337126941053</v>
+        <v>0.3916141193674077</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.089044553217243</v>
+        <v>-0.208042610545323</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1524</v>
+        <v>1474</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>494.8344686507933</v>
+        <v>504.2037480061646</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>29.95</v>
+        <v>10.25</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.07306702908024</v>
+        <v>55.23164134041306</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.23460065039131</v>
+        <v>28.31508080088525</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2846319322292868</v>
+        <v>0.4714339473541764</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.2908696762863385</v>
+        <v>0.0045903981878263</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1341</v>
+        <v>1437</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>493.3586738736569</v>
+        <v>497.3689029848045</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>62</v>
+        <v>29.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.26571175532203</v>
+        <v>59.95079616603009</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.99946568973137</v>
+        <v>26.13949434108144</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.878707329473994</v>
+        <v>0.6376628249354505</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0992162981577083</v>
+        <v>0.1481435158737044</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1537</v>
+        <v>1524</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>489.9209484337615</v>
+        <v>494.8344686507933</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>127.5</v>
+        <v>29.95</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>58.73620511604233</v>
+        <v>48.07306704454277</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.951057440364451</v>
+        <v>16.23460065039131</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6057946502716004</v>
+        <v>0.2846319322292868</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0147820587012891</v>
+        <v>-0.2908696764008172</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1452</v>
+        <v>1341</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>479.3486648378032</v>
+        <v>493.3586738736569</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>11.15</v>
+        <v>62</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>59.7412030752773</v>
+        <v>50.2657116364898</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.95128833939903</v>
+        <v>10.99946568005531</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.542091811107839</v>
+        <v>1.878707329473994</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0655651425900125</v>
+        <v>-0.09921629813862599</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1416</v>
+        <v>1452</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>475.6627656593615</v>
+        <v>479.3486648378032</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11.1</v>
+        <v>11.15</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.29208671893821</v>
+        <v>59.7412031442096</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.09270749528139</v>
+        <v>18.95128833939903</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8693758241844532</v>
+        <v>1.542091811107839</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0185744307440982</v>
+        <v>0.0655651425900125</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1225</v>
+        <v>1416</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>469.5081289041721</v>
+        <v>475.6627656593615</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>32.25</v>
+        <v>11.1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>59.15724440147043</v>
+        <v>45.29208674086332</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.48631186884588</v>
+        <v>25.09270747016262</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7508128904172097</v>
+        <v>0.8693758241844532</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.4051218759914243</v>
+        <v>-0.018574430725019</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1531</v>
+        <v>1447</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>463.3665503321565</v>
+        <v>451.3314279793832</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>12.9</v>
+        <v>6.03</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.89292333622267</v>
+        <v>50.18861129696867</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.06976093790541</v>
+        <v>31.17090116562068</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3336761861622408</v>
+        <v>0.5323135605998941</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.038353757081054</v>
+        <v>-0.0802919177022139</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1101</v>
+        <v>1460</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>458.3607668403184</v>
+        <v>447.9664600540518</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>24.5</v>
+        <v>7.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.76456285163557</v>
+        <v>53.89257654767219</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.91001706813055</v>
+        <v>14.6321740255548</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9389640708911446</v>
+        <v>0.7173800024503196</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.047235481100803</v>
+        <v>0.0064840725158421</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1447</v>
+        <v>1103</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>451.3314279793832</v>
+        <v>446.1247328722617</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>6.03</v>
+        <v>13.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.18861131037917</v>
+        <v>62.45660706279585</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31.17090121160776</v>
+        <v>15.94351070208299</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5323135605998941</v>
+        <v>0.5997460309275028</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.08029191770984601</v>
+        <v>0.0553515385723448</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>447.9664600540517</v>
+        <v>445.4267459812485</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>7.2</v>
+        <v>14.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>53.89257652418878</v>
+        <v>44.71235943981799</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.63217406716161</v>
+        <v>17.20957073376873</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7173800024503196</v>
+        <v>2.342674598124848</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0064840725196579</v>
+        <v>0.0575697905047059</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1103</v>
+        <v>1413</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>446.1247328722617</v>
+        <v>431.3410897264375</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>13.8</v>
+        <v>9.44</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>62.45660714807379</v>
+        <v>49.51334067808513</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.94351059159626</v>
+        <v>6.614917610038835</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5997460309275028</v>
+        <v>0.9296723653964544</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0553515385437251</v>
+        <v>-0.0112643344896217</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1308</v>
+        <v>1256</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>439.6601571998519</v>
+        <v>431.3045291912051</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13.95</v>
+        <v>181.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.64491995845301</v>
+        <v>49.24491147580878</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.7311134687689</v>
+        <v>21.89612076945481</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.131505124513402</v>
+        <v>0.6831323681025595</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0881924123780284</v>
+        <v>-2.208574045349883</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1256</v>
+        <v>1315</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>431.3045291912051</v>
+        <v>421.7182022320778</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>181.5</v>
+        <v>62.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.24491147580878</v>
+        <v>56.62021652055941</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.89612082304712</v>
+        <v>12.72777089981604</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6831323681025595</v>
+        <v>3.065663976084421</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.208574045349883</v>
+        <v>0.1099375537097131</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1465</v>
+        <v>1521</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>430.8765755558301</v>
+        <v>417.3278842801328</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12.5</v>
+        <v>26.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>57.66207972886363</v>
+        <v>54.29160453195838</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.39883833767165</v>
+        <v>19.91299463666361</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4828718709459609</v>
+        <v>0.5573735497188963</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0102360332661207</v>
+        <v>-0.0937303265192638</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1437</v>
+        <v>1201</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>422.3689029848045</v>
+        <v>415.1313572441856</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>29.55</v>
+        <v>12.55</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>59.95079613155299</v>
+        <v>55.59154997664239</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>26.13949427146751</v>
+        <v>25.68907097148424</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6376628249354505</v>
+        <v>0.8766406629161367</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1481435158450877</v>
+        <v>0.0476239477091845</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1315</v>
+        <v>1440</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>421.7182022320778</v>
+        <v>414.8612657245436</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>62.3</v>
+        <v>13.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.62021634784737</v>
+        <v>53.29365498468978</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.72777089637521</v>
+        <v>23.11535594751786</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.065663976084421</v>
+        <v>0.7205368078037757</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.109937553766958</v>
+        <v>-0.0278208911873492</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1521</v>
+        <v>1213</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>417.3278842801328</v>
+        <v>404.2085228280347</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>26.6</v>
+        <v>8.33</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.29160471562381</v>
+        <v>51.2941644744036</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.9129948725094</v>
+        <v>11.13904592345456</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5573735497188963</v>
+        <v>0.8917145835558813</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.09373032701533</v>
+        <v>0.1023588984353297</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1466</v>
+        <v>1517</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>415.4267459812485</v>
+        <v>399.0930316102082</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>14.3</v>
+        <v>10.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.71235956940462</v>
+        <v>54.06668945943703</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.20957065897794</v>
+        <v>21.81344643903937</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.342674598124848</v>
+        <v>0.912417240958982</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0575697904283874</v>
+        <v>0.0520074695204327</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1201</v>
+        <v>1526</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>415.1313572441856</v>
+        <v>399.0833221544994</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>12.55</v>
+        <v>14.55</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>55.59154997664239</v>
+        <v>43.04559711046511</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>25.68907088260579</v>
+        <v>22.13712446132882</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8766406629161367</v>
+        <v>0.7684686686787151</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0476239476996468</v>
+        <v>0.040652897880984</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>414.8612657245436</v>
+        <v>391.9929205170098</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>13.3</v>
+        <v>27.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.29365499955385</v>
+        <v>66.7508210942169</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.11535591550535</v>
+        <v>18.82969313868715</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7205368078037757</v>
+        <v>0.4624922850753813</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0278208912159683</v>
+        <v>0.1352967946824557</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1229</v>
+        <v>1464</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>404.4295924979664</v>
+        <v>379.3508681419255</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>41.9</v>
+        <v>10.3</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.0451948338769</v>
+        <v>49.42531546948776</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>25.35375011689799</v>
+        <v>21.90915778919362</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.947929693493524</v>
+        <v>0.8630637326166987</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1214437077558209</v>
+        <v>-0.0111766408135319</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1213</v>
+        <v>1435</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>404.2085228280347</v>
+        <v>377.3028185835054</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>8.33</v>
+        <v>14.1</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.29416447863515</v>
+        <v>52.01615144339371</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.13904601590219</v>
+        <v>8.063136071575158</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8917145835558813</v>
+        <v>1.266370439663237</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1023588984734882</v>
+        <v>0.1425275403388597</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>404.1937756948049</v>
+        <v>375.4010339967188</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>50.4</v>
+        <v>33.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.7262370213095</v>
+        <v>55.07420547307096</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>24.88772595003129</v>
+        <v>18.29289482011144</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7315098003191723</v>
+        <v>0.6767657446985732</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0805316342728196</v>
+        <v>-0.0043926283143771</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1517</v>
+        <v>1506</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>399.0930316102082</v>
+        <v>375.3061570097166</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.06668945943703</v>
+        <v>48.41168372063035</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.81344644835993</v>
+        <v>26.52111867458808</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.912417240958982</v>
+        <v>0.4686831307741343</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0520074695013533</v>
+        <v>0.0523609018830725</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1443</v>
+        <v>1217</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>391.9929205170098</v>
+        <v>372.7572149681868</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>27.9</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>66.75082585562245</v>
+        <v>55.28570957207075</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.82969315738048</v>
+        <v>22.27106263329659</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4624922850753813</v>
+        <v>0.6520740971076495</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1352967946729157</v>
+        <v>0.0161309067016838</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1526</v>
+        <v>1472</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>379.0833221544994</v>
+        <v>370.4555137799081</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>14.55</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.04559724667928</v>
+        <v>52.40144167233694</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.1371243748024</v>
+        <v>9.056578179387785</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7684686686787151</v>
+        <v>0.3455513779908061</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0406528977855871</v>
+        <v>0.4584873800473181</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>375.4010339967188</v>
+        <v>361.6070134371662</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>33.3</v>
+        <v>30.55</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>55.07420574237046</v>
+        <v>50.44762425357946</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.29289476262801</v>
+        <v>29.49427602684659</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6767657446985732</v>
+        <v>0.2649638691575833</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0043926285051697</v>
+        <v>-0.4054164471075665</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1506</v>
+        <v>1438</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>375.3061570097166</v>
+        <v>357.1452006043351</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10.3</v>
+        <v>22.25</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.41168368514126</v>
+        <v>52.60769420089458</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.52111868498566</v>
+        <v>28.8264731620782</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4686831307741343</v>
+        <v>0.5971315524864168</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0523609018830725</v>
+        <v>0.4035812283249412</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1217</v>
+        <v>1203</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>372.7572149681868</v>
+        <v>354.7451403976225</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>43</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>55.28570957207075</v>
+        <v>51.72744357064269</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>22.27106262439637</v>
+        <v>18.57749428547929</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6520740971076495</v>
+        <v>0.1922639248345938</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0161309067016838</v>
+        <v>0.0009775289035551999</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1472</v>
+        <v>1231</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>370.4555137799081</v>
+        <v>353.6995462514231</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>91</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.40144159230423</v>
+        <v>51.53770299363808</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9.056577868125029</v>
+        <v>19.93705584123946</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3455513779908061</v>
+        <v>0.5567981918613102</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.4584873805624911</v>
+        <v>0.1355616317184214</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1530</v>
+        <v>1454</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>361.6070134371662</v>
+        <v>349.0736695870559</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>30.55</v>
+        <v>12.85</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.44762428349413</v>
+        <v>47.64023045079414</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>29.49427604220825</v>
+        <v>24.05118871567157</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2649638691575833</v>
+        <v>0.332869007896855</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.4054164471266457</v>
+        <v>0.0064236140172303</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1464</v>
+        <v>1305</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>359.3508681419254</v>
+        <v>345.1881169569097</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>10.3</v>
+        <v>13.25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.42531571484378</v>
+        <v>53.66545947211333</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.9091577944697</v>
+        <v>12.1099617320226</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8630637326166987</v>
+        <v>1.246338124289308</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0111766408993893</v>
+        <v>0.092627118227432</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1476</v>
+        <v>1340</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>359.0570736615705</v>
+        <v>338.8700335824805</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>327</v>
+        <v>5.72</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.66196372436197</v>
+        <v>51.03453311062326</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.78585031742028</v>
+        <v>16.84875228618575</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.426463270214465</v>
+        <v>0.5037596417152249</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.400246121984863</v>
+        <v>0.0336176425275572</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1438</v>
+        <v>1528</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>357.1452006043351</v>
+        <v>336.5183951742151</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>22.25</v>
+        <v>25.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.60769435231945</v>
+        <v>45.32050959426256</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28.82647273531899</v>
+        <v>8.915214870525228</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5971315524864168</v>
+        <v>0.3880915368881186</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.4035812278861145</v>
+        <v>-0.1907108160880026</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1203</v>
+        <v>1467</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>354.7451403976225</v>
+        <v>334.6507176597547</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>43</v>
+        <v>7.28</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.72744360843749</v>
+        <v>46.95046518961541</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.57749427569886</v>
+        <v>29.73270199406217</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.1922639248345938</v>
+        <v>0.577164341193007</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0009775289130888</v>
+        <v>-0.035580145999719</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>353.6995462514231</v>
+        <v>334.5624817251229</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>51.5377030587604</v>
+        <v>42.89466189562577</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.93705585045925</v>
+        <v>28.89339861947294</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5567981918613102</v>
+        <v>0.5429912998535098</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1355616314322285</v>
+        <v>0.031014080431561</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1454</v>
+        <v>1418</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>349.0736695870559</v>
+        <v>330.2379994094288</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.85</v>
+        <v>18.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>47.64023047431558</v>
+        <v>49.26127743026068</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>24.05118868676196</v>
+        <v>24.40318894346667</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.332869007896855</v>
+        <v>0.3428776340162555</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0064236140267683</v>
+        <v>-0.0046080205085807</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1305</v>
+        <v>1108</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>345.1881169569097</v>
+        <v>329.2598410072911</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>13.25</v>
+        <v>13.9</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>53.66545946366191</v>
+        <v>49.84830139789614</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.10996178042984</v>
+        <v>31.89090345430081</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.246338124289308</v>
+        <v>0.3593337663392648</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.09262711821789139</v>
+        <v>0.052998925489842</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1528</v>
+        <v>1512</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>336.5183951742151</v>
+        <v>326.0500249839791</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.4</v>
+        <v>7.25</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.3205095865666</v>
+        <v>58.46872544684311</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>8.915214879444607</v>
+        <v>10.96966951410226</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3880915368881186</v>
+        <v>1.416511479762644</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1907108160975439</v>
+        <v>0.0426032847462061</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1467</v>
+        <v>1324</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>334.6507176597547</v>
+        <v>312.5690281201718</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>7.28</v>
+        <v>10.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.95046518961541</v>
+        <v>46.67001983775374</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>29.73270200320617</v>
+        <v>22.64983927564736</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.577164341193007</v>
+        <v>2.047306422170674</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0355801460035351</v>
+        <v>0.0124484818087332</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1219</v>
+        <v>1470</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>334.5624817251229</v>
+        <v>311.7085454462015</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.89466200168309</v>
+        <v>35.30734962947267</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>28.89339858289667</v>
+        <v>12.74841716738727</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5429912998535098</v>
+        <v>0.0056849451765659</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0310140804029417</v>
+        <v>-1.438726190395205</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1418</v>
+        <v>1316</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>330.2379994094288</v>
+        <v>311.612045199291</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>18.5</v>
+        <v>10.95</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.26127751370088</v>
+        <v>52.06757724934013</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>24.40318893528406</v>
+        <v>20.39008776163514</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3428776340162555</v>
+        <v>0.6861769947223996</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0046080205276598</v>
+        <v>0.101038116706495</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1108</v>
+        <v>1516</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>329.2598410072911</v>
+        <v>307.4564520343147</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>13.9</v>
+        <v>20.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.84830142211924</v>
+        <v>43.99715183782658</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>31.8909033856577</v>
+        <v>15.89886142518246</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3593337663392648</v>
+        <v>0.5621324648423434</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0529989254707615</v>
+        <v>-0.0739357179128407</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1512</v>
+        <v>1529</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>326.0500249839791</v>
+        <v>291.491074206124</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>7.25</v>
+        <v>22.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>58.46872540304839</v>
+        <v>52.38935809628039</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10.96966944289449</v>
+        <v>18.58350321730451</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.416511479762644</v>
+        <v>0.5801214237898505</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0426032847442971</v>
+        <v>0.0507438717363569</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1413</v>
+        <v>1582</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>321.3410897264375</v>
+        <v>283.1826076335977</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>9.44</v>
+        <v>93.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.51334061605633</v>
+        <v>44.24367230531747</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>6.614917588641307</v>
+        <v>21.87882572903472</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9296723653964544</v>
+        <v>0.3471153347949783</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0112643344896217</v>
+        <v>-1.839261504536931</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1470</v>
+        <v>1522</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>311.7085454462015</v>
+        <v>281.6444765222221</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.30734960164682</v>
+        <v>54.41192127909954</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.74841715854758</v>
+        <v>16.884223158752</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.0056849451765659</v>
+        <v>0.7004570992660725</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.438726190442905</v>
+        <v>0.0685819936162286</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1316</v>
+        <v>1215</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>311.6120451992911</v>
+        <v>278.528638241205</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>10.95</v>
+        <v>115</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.06757726197096</v>
+        <v>31.35571844374053</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.39008768225057</v>
+        <v>42.54680098601817</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6861769947223996</v>
+        <v>0.6249992823161552</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1010381167255746</v>
+        <v>0.111636434297841</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1516</v>
+        <v>1441</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>307.4564520343147</v>
+        <v>257.3797088412625</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.5</v>
+        <v>9.25</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.99715183165405</v>
+        <v>43.41937497839606</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.89886142357627</v>
+        <v>15.39298727831139</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5621324648423434</v>
+        <v>0.2197384500476081</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0739357178937607</v>
+        <v>0.0199911622907344</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1540</v>
+        <v>1417</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>305.4431066212883</v>
+        <v>252.86159507928</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>21.9</v>
+        <v>8.52</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.7482925226533</v>
+        <v>53.64188323962764</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.9315040070865</v>
+        <v>18.10230499419437</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5763318913027298</v>
+        <v>1.034239343469995</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0244850624260352</v>
+        <v>0.0399927031155317</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1215</v>
+        <v>1459</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>293.528638241205</v>
+        <v>250.186030754045</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>115</v>
+        <v>11.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>31.35571840045675</v>
+        <v>52.85089422884813</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>42.54680098620835</v>
+        <v>15.61608054271682</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6249992823161552</v>
+        <v>0.1962857796854811</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1116364343932385</v>
+        <v>0.0195901217367808</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1324</v>
+        <v>1232</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>292.5690281201718</v>
+        <v>231.1636457190954</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>10.4</v>
+        <v>143</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.67001983775374</v>
+        <v>30.72937857515684</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.64983932098058</v>
+        <v>23.20996608549361</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.047306422170674</v>
+        <v>1.230859198708374</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0124484817896536</v>
+        <v>-0.5994606080134155</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1522</v>
+        <v>1439</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>281.6444765222221</v>
+        <v>223.7675599585726</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>32.1</v>
+        <v>25.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>54.41192131072905</v>
+        <v>49.60016602858487</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.88422315337019</v>
+        <v>4.66953999105348</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7004570992660725</v>
+        <v>0.0225280276824404</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0685819936162286</v>
+        <v>-0.0071942910054995</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1558</v>
+        <v>1463</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>271.9423747476848</v>
+        <v>218.0984508592308</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>91.5</v>
+        <v>17.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>54.08258869726802</v>
+        <v>41.98724611543204</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.47863260299906</v>
+        <v>10.67165676068855</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.8615121072072233</v>
+        <v>0.9686308257880925</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0872922281804929</v>
+        <v>0.001250854821777</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1529</v>
+        <v>1218</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>271.491074206125</v>
+        <v>206.5916516356558</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>22.9</v>
+        <v>17.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.38935809143221</v>
+        <v>30.98472265949025</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.58350318753211</v>
+        <v>28.37945090179172</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5801214237898505</v>
+        <v>0.8591651635655844</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0507438717268138</v>
+        <v>-0.1570264975334555</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1536</v>
+        <v>1473</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>269.3063430111831</v>
+        <v>200.4286929516823</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>48.7</v>
+        <v>20.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.9832184069942</v>
+        <v>38.30558541494312</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.382603520038</v>
+        <v>20.75580764590497</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4394219457263302</v>
+        <v>0.9254436722074634</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1728504947379672</v>
+        <v>-0.0092111950266381</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1538</v>
+        <v>1519</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>266.4550499594624</v>
+        <v>197.695441498276</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,49 +6064,49 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>37.94587831936163</v>
+        <v>49.81773353165728</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6.44127393331766</v>
+        <v>11.80543860474762</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.0933335741941699</v>
+        <v>0.8292367848057336</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.5293624812840951</v>
+        <v>-2.605913246909886</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>257.3797088412625</v>
+        <v>197.4079620251212</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>9.25</v>
+        <v>10.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.41937499841645</v>
+        <v>48.24542337747956</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.39298729489184</v>
+        <v>14.45126524436638</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2197384500476081</v>
+        <v>1.235946107168569</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0199911622907344</v>
+        <v>0.0144767122112801</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1417</v>
+        <v>1309</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>252.8615950792801</v>
+        <v>194.395839303827</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>8.52</v>
+        <v>14.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>53.64188324781609</v>
+        <v>40.19815916056525</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.10230499372401</v>
+        <v>11.9217503575635</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.034239343469995</v>
+        <v>0.6817886332992179</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0399927031117154</v>
+        <v>-0.0296626664879235</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1459</v>
+        <v>1323</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>250.186030754045</v>
+        <v>192.9425132487936</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>11.8</v>
+        <v>19.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.85089419772513</v>
+        <v>46.81658869391678</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.61608059976116</v>
+        <v>14.42203888963332</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1962857796854811</v>
+        <v>0.9577574295683942</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0195901217177015</v>
+        <v>-0.0224389009582607</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1232</v>
+        <v>1109</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>231.1636457190954</v>
+        <v>188.1563542731412</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>143</v>
+        <v>14.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>30.72937857515684</v>
+        <v>43.18916699277757</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>23.20996603132871</v>
+        <v>24.54063856724948</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.230859198708374</v>
+        <v>1.392091312012331</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.5994606079180103</v>
+        <v>0.0261661743344631</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1340</v>
+        <v>1233</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>228.8700335824805</v>
+        <v>172.6575533082148</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>5.72</v>
+        <v>28</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>51.03453310536955</v>
+        <v>47.33900472060665</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.84875228618575</v>
+        <v>18.65928798531922</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5037596417152249</v>
+        <v>0.3374256644367731</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0336176425275572</v>
+        <v>0.06963801728022639</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1439</v>
+        <v>1457</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>223.7675599585726</v>
+        <v>172.1553085539658</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>25.3</v>
+        <v>14.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>49.60016599989496</v>
+        <v>45.512055394927</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>4.669540119534124</v>
+        <v>19.99132615262341</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.0225280276824404</v>
+        <v>0.8348609736415091</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0071942909864183</v>
+        <v>-0.0147298748087928</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1463</v>
+        <v>1220</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>218.0984508592309</v>
+        <v>171.9042477952381</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.6</v>
+        <v>11.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>41.98724578227862</v>
+        <v>38.38382357076729</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>10.67165674474283</v>
+        <v>30.30191371637733</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9686308257880925</v>
+        <v>0.5942116369070093</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0012508548408569</v>
+        <v>0.0183385446838285</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1218</v>
+        <v>1451</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>206.5916516356558</v>
+        <v>171.6909591493734</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>17.9</v>
+        <v>16.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>30.98472260872958</v>
+        <v>49.31627723615088</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>28.37945089381182</v>
+        <v>11.17032851585702</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8591651635655844</v>
+        <v>0.5584919651855531</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1570264975239145</v>
+        <v>0.0453369316386756</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>200.4286929516823</v>
+        <v>159.8703921308577</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>20.2</v>
+        <v>12</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.30558547115292</v>
+        <v>49.48317207004429</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.7558074772326</v>
+        <v>9.356195427416788</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.9254436722074634</v>
+        <v>1.332329260188842</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.009211195122035901</v>
+        <v>0.0149295173073751</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1519</v>
+        <v>1569</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>197.695441498276</v>
+        <v>153.992834816581</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>833</v>
+        <v>48.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>49.81773354637036</v>
+        <v>41.03348304742002</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.80543862113011</v>
+        <v>14.1495462379899</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8292367848057336</v>
+        <v>0.5156235209366679</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-2.605913249008546</v>
+        <v>-0.0932497315529958</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1471</v>
+        <v>1410</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>197.4079620251212</v>
+        <v>131.0032214725879</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10.95</v>
+        <v>24.85</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>48.24542340919679</v>
+        <v>34.2869672304565</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.45126513881168</v>
+        <v>15.14909258404206</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.235946107168569</v>
+        <v>0.5409608012391172</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.014476712163581</v>
+        <v>0.0231260323310376</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1309</v>
+        <v>1445</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>194.395839303827</v>
+        <v>81.55552797341271</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14.75</v>
+        <v>11</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.1981591670168</v>
+        <v>31.57245759113273</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.92175041899452</v>
+        <v>14.86745737527452</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6817886332992179</v>
+        <v>0.7572572916786937</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0296626665260809</v>
+        <v>-0.0119745482591869</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>192.9425132487936</v>
+        <v>81.2224697907068</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>19.8</v>
+        <v>26.1</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.8165887689086</v>
+        <v>43.9608806912912</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.42203887261307</v>
+        <v>12.8241025191739</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.9577574295683942</v>
+        <v>0.6294322188050135</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,751 +6771,9 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0224389010155006</v>
+        <v>-0.0464958818346795</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>1582</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>信錦</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>188.1826076335977</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>44.24367229309753</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>21.87882564530146</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>0.3471153347949783</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>-1.839261504689575</v>
-      </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>1109</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>信大</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>188.1563542731412</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>43.189166834525</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>24.54063847970393</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>1.392091312012331</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>0.0261661743344631</v>
-      </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>錩泰</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>179.9019545869861</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>52.79166445466077</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>13.15554848146344</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0.3772725183801061</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>0.1845861303733657</v>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>1435</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>中福</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>177.3028185835055</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>52.01615171525238</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>8.063136083426691</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>1.266370439663237</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>0.1425275393311431</v>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>1233</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>天仁</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>172.6575533082148</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>47.33900491833093</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>18.65928745530725</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>0.3374256644367731</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>0.06963801713712719</v>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>1457</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>宜進</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>172.1553085539658</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>45.51205537834942</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>19.99132615044786</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>0.8348609736415091</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>-0.0147298748183293</v>
-      </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>1220</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>台榮</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>171.9042477952381</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>38.38382339303581</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>30.30191365963445</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>0.5942116369070093</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>0.0183385446838285</v>
-      </c>
-      <c r="O126" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>1451</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>年興</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>171.6909591493736</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>49.31627728501832</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>11.17032854210724</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>0.5584919651855531</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>0.0453369316100559</v>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>1468</v>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>昶和</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>159.8703921308578</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>49.48317207004429</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>9.356195449528022</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>1.332329260188842</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N128" s="2" t="n">
-        <v>0.0149295173073751</v>
-      </c>
-      <c r="O128" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>1569</v>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>濱川</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>153.992834816581</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>41.03348315567674</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>14.14954619068666</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>0.5156235209366679</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>-0.0932497318773402</v>
-      </c>
-      <c r="O129" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>1410</v>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>南染</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>131.0032214725879</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>34.2869672304565</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>15.14909258149443</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>0.5409608012391172</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N130" s="2" t="n">
-        <v>0.0231260323405755</v>
-      </c>
-      <c r="O130" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>1445</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>大宇</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>81.55552797341259</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>31.57245757770704</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>14.86745733935442</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>0.7572572916786937</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N131" s="2" t="n">
-        <v>-0.0119745482496475</v>
-      </c>
-      <c r="O131" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>1325</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>恆大</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>61.22246979071885</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>43.96088063479276</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>12.82410250791465</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>0.6294322188050135</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>-0.0464958819300742</v>
-      </c>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>1539</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>巨庭</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>60.97046950837708</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>45.20967869267656</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>18.27485933911214</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>0.5764937850685035</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>-0.0366568058249175</v>
-      </c>
-      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq1_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1503</v>
+        <v>1210</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>892.7061157387524</v>
+        <v>854.5497812820505</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>241.5</v>
+        <v>54.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.61356524461225</v>
+        <v>56.00850916201571</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.42477104101332</v>
+        <v>28.29750800717133</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.8997420603596417</v>
+        <v>0.5941407308952612</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0577965948213785</v>
+        <v>0.1376317583020645</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1455</v>
+        <v>1342</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>863.8000379800418</v>
+        <v>815.7538899352642</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10.2</v>
+        <v>116</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.07598197540156</v>
+        <v>72.52214129145692</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>43.02226714854736</v>
+        <v>41.98778044201702</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.197635395191481</v>
+        <v>0.9947541827124956</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0671395500903484</v>
+        <v>1.485242999900608</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1210</v>
+        <v>1307</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>854.5497812820505</v>
+        <v>802.2601313372636</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54.7</v>
+        <v>36.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.00850916201571</v>
+        <v>68.82540943480555</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28.29750800717133</v>
+        <v>30.89402956076432</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5941407308952612</v>
+        <v>0.5260131337263608</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1376317583020645</v>
+        <v>0.2988626560117808</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1342</v>
+        <v>1236</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>815.7538899352642</v>
+        <v>797.8456021055274</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116</v>
+        <v>25.8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>72.52214129145692</v>
+        <v>63.21876149397025</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>41.98778044201702</v>
+        <v>14.97363160233272</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9947541827124956</v>
+        <v>3.05312651146466</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.485242999900608</v>
+        <v>0.1159850736446855</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1513</v>
+        <v>1436</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>803.4700676590958</v>
+        <v>748.7050098124354</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>176.5</v>
+        <v>47.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.67521166497431</v>
+        <v>55.5234829461923</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.14224504369142</v>
+        <v>29.5980696850501</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8880220477980655</v>
+        <v>1.682746045526478</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.1196359775771456</v>
+        <v>0.4113201450827294</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>802.2601313372636</v>
+        <v>736.3122637934827</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>36.4</v>
+        <v>13.55</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.82540943480555</v>
+        <v>56.82189578120946</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.89402956076432</v>
+        <v>17.43802983977482</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5260131337263608</v>
+        <v>1.36337126941053</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2988626560117808</v>
+        <v>0.08904455322678299</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1236</v>
+        <v>1339</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>797.8456021055274</v>
+        <v>726.242673475292</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.8</v>
+        <v>43.95</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.21876149397025</v>
+        <v>55.03984517232819</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.97363160233272</v>
+        <v>25.37716800699772</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.05312651146466</v>
+        <v>0.7716085142239336</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1159850736446855</v>
+        <v>-0.0266077430382258</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>748.7050098124354</v>
+        <v>725.0816647553238</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>47.5</v>
+        <v>17.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.5234829461923</v>
+        <v>66.1443518782105</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>29.5980696850501</v>
+        <v>22.35439014996757</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.682746045526478</v>
+        <v>2.153957115632234</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.4113201450827294</v>
+        <v>0.06502627600529511</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>736.3122637934827</v>
+        <v>699.5396528141365</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.55</v>
+        <v>11.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.82189578120946</v>
+        <v>59.40777970188018</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>17.43802983977482</v>
+        <v>19.53659650926148</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.36337126941053</v>
+        <v>1.047899710641487</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.08904455322678299</v>
+        <v>0.07192872993325421</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1339</v>
+        <v>1434</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>726.242673475292</v>
+        <v>692.8838996269352</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>43.95</v>
+        <v>16.95</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.03984517232819</v>
+        <v>65.99272823920637</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.37716800699772</v>
+        <v>25.92622368880813</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.7716085142239336</v>
+        <v>0.920412451593225</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.0266077430382258</v>
+        <v>0.1077369110086075</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1432</v>
+        <v>1338</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>725.0816647553238</v>
+        <v>686.0157226220391</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>66.1443518782105</v>
+        <v>60.37026794230912</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.35439014996757</v>
+        <v>21.52508560192718</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.153957115632234</v>
+        <v>0.2960259134605936</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.06502627600529511</v>
+        <v>0.0667006189894196</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1456</v>
+        <v>1321</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>723.5060746387871</v>
+        <v>678.3656810588507</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15.5</v>
+        <v>32.15</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>71.73396626291438</v>
+        <v>68.33980308725089</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.70634066446499</v>
+        <v>44.5098725515812</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.45060746387871</v>
+        <v>1.440236062360517</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2194367130684937</v>
+        <v>0.3848319477861786</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1525</v>
+        <v>1402</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>701.5406374380354</v>
+        <v>676.5070199521294</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>66</v>
+        <v>28.85</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>51.98658037841993</v>
+        <v>63.03970351754613</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.27099740091602</v>
+        <v>18.29242953046834</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2254912162044985</v>
+        <v>0.5014713294127671</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.4187585458299818</v>
+        <v>0.2309345337692722</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>699.5396528141365</v>
+        <v>659.6088013199532</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11.6</v>
+        <v>99.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.40777970188018</v>
+        <v>57.42020484759104</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19.53659650926148</v>
+        <v>36.27035655853308</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.047899710641487</v>
+        <v>1.252047492523111</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.07192872993325421</v>
+        <v>0.09856468346116461</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1515</v>
+        <v>1444</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>699.3100456859476</v>
+        <v>657.5542567724973</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>25.9</v>
+        <v>7.04</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.43587110969604</v>
+        <v>58.84261111634376</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.7993265557867</v>
+        <v>33.4810933077659</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.031004568594761</v>
+        <v>0.4787007153984733</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2364530078577263</v>
+        <v>0.0153050651076618</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1434</v>
+        <v>1102</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>692.8838996269352</v>
+        <v>652.8802183208379</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16.95</v>
+        <v>35.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>65.99272823920637</v>
+        <v>63.25795357631394</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.92622368880813</v>
+        <v>16.24054038084162</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.920412451593225</v>
+        <v>0.7292745764137463</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1077369110086075</v>
+        <v>0.2460159324520993</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1338</v>
+        <v>1310</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>686.0157226220391</v>
+        <v>649.2035235197391</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>17.2</v>
+        <v>9.26</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.37026794230912</v>
+        <v>60.10062592635524</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.52508560192718</v>
+        <v>20.17743653583982</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.2960259134605936</v>
+        <v>2.376397343442056</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0667006189894196</v>
+        <v>0.0876633298989556</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1321</v>
+        <v>1216</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>678.3656810588507</v>
+        <v>647.4525091711652</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32.15</v>
+        <v>74.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>68.33980308725089</v>
+        <v>53.14904454895826</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44.5098725515812</v>
+        <v>20.76337920467265</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.440236062360517</v>
+        <v>1.569797742192853</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3848319477861786</v>
+        <v>0.1498669317323347</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1402</v>
+        <v>1419</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>676.5070199521294</v>
+        <v>640.7799540690776</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>28.85</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.03970351754613</v>
+        <v>57.42886703956965</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.29242953046834</v>
+        <v>21.54105185696687</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5014713294127671</v>
+        <v>0.4701577426923286</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2309345337692722</v>
+        <v>0.117014034272866</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1319</v>
+        <v>1409</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>659.6088013199532</v>
+        <v>624.8202770200872</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>99.2</v>
+        <v>25.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.42020484759104</v>
+        <v>58.86688740500579</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>36.27035655853308</v>
+        <v>33.90228862072883</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.252047492523111</v>
+        <v>1.645819034232483</v>
       </c>
       <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.09856468346116461</v>
+        <v>-0.0691676826753822</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1444</v>
+        <v>1312</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>657.5542567724973</v>
+        <v>620.3260340202017</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>7.04</v>
+        <v>13.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.84261111634376</v>
+        <v>58.90061377914206</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.4810933077659</v>
+        <v>30.0566255908111</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4787007153984733</v>
+        <v>0.5972918402774777</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0153050651076618</v>
+        <v>0.0500154251928375</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1102</v>
+        <v>1227</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>652.8802183208379</v>
+        <v>612.2643517411922</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>35.8</v>
+        <v>29.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.25795357631394</v>
+        <v>56.73017837542036</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.24054038084162</v>
+        <v>18.7680127063311</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7292745764137463</v>
+        <v>0.9092581356694578</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2460159324520993</v>
+        <v>0.1147458914991183</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1310</v>
+        <v>1225</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>649.2035235197391</v>
+        <v>609.5081289041721</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>9.26</v>
+        <v>32.25</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>60.10062592635524</v>
+        <v>59.15724440147043</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.17743653583982</v>
+        <v>21.48631186884588</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.376397343442056</v>
+        <v>0.7508128904172097</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0876633298989556</v>
+        <v>0.4051218759914243</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1216</v>
+        <v>1446</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>647.4525091711652</v>
+        <v>605.9669472862163</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>74.5</v>
+        <v>16.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>53.14904454895826</v>
+        <v>60.10552185122149</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.76337920467265</v>
+        <v>26.75096354072749</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.569797742192853</v>
+        <v>0.7044634451767535</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1498669317323347</v>
+        <v>0.0408561489174495</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1419</v>
+        <v>1104</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>640.7799540690776</v>
+        <v>584.5331908379574</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.42886703956965</v>
+        <v>62.09469360791442</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.54105185696687</v>
+        <v>31.08434188280217</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4701577426923286</v>
+        <v>1.673098637683775</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.117014034272866</v>
+        <v>0.077195968919125</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1409</v>
+        <v>1314</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>624.8202770200872</v>
+        <v>580.2895479050012</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>25.6</v>
+        <v>7.78</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.86688740500579</v>
+        <v>55.23069085151434</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.90228862072883</v>
+        <v>15.09222657468816</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.645819034232483</v>
+        <v>0.6112692406684329</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0691676826753822</v>
+        <v>0.0040936721384182</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1312</v>
+        <v>1101</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>620.3260340202017</v>
+        <v>573.4302563936706</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>13.5</v>
+        <v>24.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.90061377914206</v>
+        <v>51.76456283138577</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.0566255908111</v>
+        <v>14.91001708951427</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5972918402774777</v>
+        <v>0.9638060972957572</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0500154251928375</v>
+        <v>0.0472354811198828</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1475</v>
+        <v>1308</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>618.7254215845575</v>
+        <v>559.6601571998519</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>27.4</v>
+        <v>13.95</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.00758688017953</v>
+        <v>53.64491994868592</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.6007751814056</v>
+        <v>14.73111346876891</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.992961267887884</v>
+        <v>1.131505124513402</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2629530789050555</v>
+        <v>0.0881924123875675</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1227</v>
+        <v>1414</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>612.2643517411922</v>
+        <v>549.8241619591524</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>29.1</v>
+        <v>17.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.73017837542036</v>
+        <v>64.79735522798596</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.7680127063311</v>
+        <v>25.69874319390791</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9092581356694578</v>
+        <v>0.3910277401585884</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1147458914991183</v>
+        <v>0.1932562636720068</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1225</v>
+        <v>1110</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>609.5081289041721</v>
+        <v>547.9092829079705</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>32.25</v>
+        <v>15.55</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>59.15724440147043</v>
+        <v>57.18459198908</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.48631186884588</v>
+        <v>32.88317198925517</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7508128904172097</v>
+        <v>0.6772333045779196</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.4051218759914243</v>
+        <v>0.0629090938443119</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>605.9669472862163</v>
+        <v>523.9317216144625</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>16.7</v>
+        <v>28</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>60.10552185122149</v>
+        <v>57.30938267660233</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.75096354072749</v>
+        <v>21.4077746077942</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7044634451767535</v>
+        <v>0.8837519370650183</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0408561489174495</v>
+        <v>0.138259192702071</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1104</v>
+        <v>1229</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>584.5331908379574</v>
+        <v>514.4295924979665</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>29.1</v>
+        <v>41.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>62.09469360791442</v>
+        <v>54.04519475643837</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.08434188280217</v>
+        <v>25.35375012840548</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.673098637683775</v>
+        <v>0.947929693493524</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.077195968919125</v>
+        <v>0.1214437077844433</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1314</v>
+        <v>1423</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>580.2895479050012</v>
+        <v>507.9161411936741</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>7.78</v>
+        <v>39.65</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.23069085151434</v>
+        <v>33.13793386110925</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15.09222657468816</v>
+        <v>28.26850913452445</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6112692406684329</v>
+        <v>0.3916141193674077</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0040936721384182</v>
+        <v>-0.208042610545323</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1101</v>
+        <v>1437</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>573.4302563936706</v>
+        <v>497.3689029848045</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>24.5</v>
+        <v>29.55</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.76456283138577</v>
+        <v>59.95079616603009</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.91001708951427</v>
+        <v>26.13949434108144</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9638060972957572</v>
+        <v>0.6376628249354505</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0472354811198828</v>
+        <v>0.1481435158737044</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1477</v>
+        <v>1341</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>571.5466910334386</v>
+        <v>493.3586738736569</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>221.5</v>
+        <v>62</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.31852108141658</v>
+        <v>50.2657116364898</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.21489132688848</v>
+        <v>10.99946568005531</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.652671112942963</v>
+        <v>1.878707329473994</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.2581856510711137</v>
+        <v>-0.09921629813862599</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1308</v>
+        <v>1416</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>559.6601571998519</v>
+        <v>475.6627656593615</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>13.95</v>
+        <v>11.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>53.64491994868592</v>
+        <v>45.29208674086332</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.73111346876891</v>
+        <v>25.09270747016262</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.131505124513402</v>
+        <v>0.8693758241844532</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0881924123875675</v>
+        <v>-0.018574430725019</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1414</v>
+        <v>1103</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>549.8241619591524</v>
+        <v>446.1247328722617</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>17.5</v>
+        <v>13.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>64.79735522798596</v>
+        <v>62.45660706279585</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25.69874319390791</v>
+        <v>15.94351070208299</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3910277401585884</v>
+        <v>0.5997460309275028</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.1932562636720068</v>
+        <v>0.0553515385723448</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1476</v>
+        <v>1413</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>549.0748523148882</v>
+        <v>431.3410897264375</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>327</v>
+        <v>9.44</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>40.66196375066807</v>
+        <v>49.51334067808513</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.78585032809397</v>
+        <v>6.614917610038835</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.427371551081816</v>
+        <v>0.9296723653964544</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.400246122748035</v>
+        <v>-0.0112643344896217</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1110</v>
+        <v>1256</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>547.9092829079705</v>
+        <v>431.3045291912051</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15.55</v>
+        <v>181.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.18459198908</v>
+        <v>49.24491147580878</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>32.88317198925517</v>
+        <v>21.89612076945481</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6772333045779196</v>
+        <v>0.6831323681025595</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0629090938443119</v>
+        <v>-2.208574045349883</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1514</v>
+        <v>1315</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>547.0340572788253</v>
+        <v>421.7182022320778</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>121.5</v>
+        <v>62.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.9598732746133</v>
+        <v>56.62021652055941</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.34844941935013</v>
+        <v>12.72777089981604</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3473575093056278</v>
+        <v>3.065663976084421</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.30619983612317</v>
+        <v>0.1099375537097131</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1465</v>
+        <v>1201</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>540.8765755558298</v>
+        <v>415.1313572441856</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12.5</v>
+        <v>12.55</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.66207980402617</v>
+        <v>55.59154997664239</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14.39883835428248</v>
+        <v>25.68907097148424</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4828718709459609</v>
+        <v>0.8766406629161367</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0102360332756602</v>
+        <v>0.0476239477091845</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1453</v>
+        <v>1440</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>531.988111470459</v>
+        <v>414.8612657245436</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.93735087282981</v>
+        <v>53.29365498468978</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>27.90554225387556</v>
+        <v>23.11535594751786</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4988111470458976</v>
+        <v>0.7205368078037757</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.07786396424651019</v>
+        <v>-0.0278208911873492</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1442</v>
+        <v>1213</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>523.9317216144625</v>
+        <v>404.2085228280347</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>28</v>
+        <v>8.33</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.30938267660233</v>
+        <v>51.2941644744036</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.4077746077942</v>
+        <v>11.13904592345456</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8837519370650183</v>
+        <v>0.8917145835558813</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.138259192702071</v>
+        <v>0.1023588984353297</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1229</v>
+        <v>1443</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>514.4295924979665</v>
+        <v>391.9929205170098</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>41.9</v>
+        <v>27.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.04519475643837</v>
+        <v>66.7508210942169</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.35375012840548</v>
+        <v>18.82969313868715</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.947929693493524</v>
+        <v>0.4624922850753813</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1214437077844433</v>
+        <v>0.1352967946824557</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1504</v>
+        <v>1435</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>512.1720945122786</v>
+        <v>377.3028185835054</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>70</v>
+        <v>14.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.16487611591501</v>
+        <v>52.01615144339371</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21.95656548367733</v>
+        <v>8.063136071575158</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4153806981740384</v>
+        <v>1.266370439663237</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.9550825539175456</v>
+        <v>0.1425275403388597</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1423</v>
+        <v>1217</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>507.9161411936741</v>
+        <v>372.7572149681868</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>39.65</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>33.13793386110925</v>
+        <v>55.28570957207075</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28.26850913452445</v>
+        <v>22.27106263329659</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3916141193674077</v>
+        <v>0.6520740971076495</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.208042610545323</v>
+        <v>0.0161309067016838</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1474</v>
+        <v>1438</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>504.2037480061646</v>
+        <v>357.1452006043351</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>10.25</v>
+        <v>22.25</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.23164134041306</v>
+        <v>52.60769420089458</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.31508080088525</v>
+        <v>28.8264731620782</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4714339473541764</v>
+        <v>0.5971315524864168</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0045903981878263</v>
+        <v>0.4035812283249412</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1437</v>
+        <v>1203</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>497.3689029848045</v>
+        <v>354.7451403976225</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>29.55</v>
+        <v>43</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>59.95079616603009</v>
+        <v>51.72744357064269</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>26.13949434108144</v>
+        <v>18.57749428547929</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6376628249354505</v>
+        <v>0.1922639248345938</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1481435158737044</v>
+        <v>0.0009775289035551999</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1524</v>
+        <v>1231</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>494.8344686507933</v>
+        <v>353.6995462514231</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>29.95</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.07306704454277</v>
+        <v>51.53770299363808</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.23460065039131</v>
+        <v>19.93705584123946</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2846319322292868</v>
+        <v>0.5567981918613102</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2908696764008172</v>
+        <v>0.1355616317184214</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1341</v>
+        <v>1305</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>493.3586738736569</v>
+        <v>345.1881169569097</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>62</v>
+        <v>13.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.2657116364898</v>
+        <v>53.66545947211333</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10.99946568005531</v>
+        <v>12.1099617320226</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.878707329473994</v>
+        <v>1.246338124289308</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.09921629813862599</v>
+        <v>0.092627118227432</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1452</v>
+        <v>1340</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>479.3486648378032</v>
+        <v>338.8700335824805</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11.15</v>
+        <v>5.72</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>59.7412031442096</v>
+        <v>51.03453311062326</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.95128833939903</v>
+        <v>16.84875228618575</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.542091811107839</v>
+        <v>0.5037596417152249</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0655651425900125</v>
+        <v>0.0336176425275572</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1416</v>
+        <v>1219</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>475.6627656593615</v>
+        <v>334.5624817251229</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>11.1</v>
+        <v>12.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.29208674086332</v>
+        <v>42.89466189562577</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25.09270747016262</v>
+        <v>28.89339861947294</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8693758241844532</v>
+        <v>0.5429912998535098</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.018574430725019</v>
+        <v>0.031014080431561</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1447</v>
+        <v>1418</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>451.3314279793832</v>
+        <v>330.2379994094288</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>6.03</v>
+        <v>18.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.18861129696867</v>
+        <v>49.26127743026068</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>31.17090116562068</v>
+        <v>24.40318894346667</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5323135605998941</v>
+        <v>0.3428776340162555</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0802919177022139</v>
+        <v>-0.0046080205085807</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1460</v>
+        <v>1108</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>447.9664600540518</v>
+        <v>329.2598410072911</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>7.2</v>
+        <v>13.9</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>53.89257654767219</v>
+        <v>49.84830139789614</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.6321740255548</v>
+        <v>31.89090345430081</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7173800024503196</v>
+        <v>0.3593337663392648</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0064840725158421</v>
+        <v>0.052998925489842</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1103</v>
+        <v>1324</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>446.1247328722617</v>
+        <v>312.5690281201718</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>62.45660706279585</v>
+        <v>46.67001983775374</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15.94351070208299</v>
+        <v>22.64983927564736</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5997460309275028</v>
+        <v>2.047306422170674</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0553515385723448</v>
+        <v>0.0124484818087332</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1466</v>
+        <v>1316</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>445.4267459812485</v>
+        <v>311.612045199291</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>14.3</v>
+        <v>10.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.71235943981799</v>
+        <v>52.06757724934013</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.20957073376873</v>
+        <v>20.39008776163514</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.342674598124848</v>
+        <v>0.6861769947223996</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0575697905047059</v>
+        <v>0.101038116706495</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1413</v>
+        <v>1529</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>431.3410897264375</v>
+        <v>291.491074206124</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>9.44</v>
+        <v>22.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.51334067808513</v>
+        <v>52.38935809628039</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>6.614917610038835</v>
+        <v>18.58350321730451</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9296723653964544</v>
+        <v>0.5801214237898505</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0112643344896217</v>
+        <v>0.0507438717363569</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1256</v>
+        <v>1582</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>431.3045291912051</v>
+        <v>283.1826076335977</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>181.5</v>
+        <v>93.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.24491147580878</v>
+        <v>44.24367230531747</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.89612076945481</v>
+        <v>21.87882572903472</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6831323681025595</v>
+        <v>0.3471153347949783</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.208574045349883</v>
+        <v>-1.839261504536931</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1315</v>
+        <v>1215</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>421.7182022320778</v>
+        <v>278.528638241205</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>62.3</v>
+        <v>115</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>56.62021652055941</v>
+        <v>31.35571844374053</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.72777089981604</v>
+        <v>42.54680098601817</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3.065663976084421</v>
+        <v>0.6249992823161552</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1099375537097131</v>
+        <v>0.111636434297841</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1521</v>
+        <v>1441</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>417.3278842801328</v>
+        <v>257.3797088412625</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>26.6</v>
+        <v>9.25</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.29160453195838</v>
+        <v>43.41937497839606</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.91299463666361</v>
+        <v>15.39298727831139</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5573735497188963</v>
+        <v>0.2197384500476081</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0937303265192638</v>
+        <v>0.0199911622907344</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1201</v>
+        <v>1417</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>415.1313572441856</v>
+        <v>252.86159507928</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12.55</v>
+        <v>8.52</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>55.59154997664239</v>
+        <v>53.64188323962764</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>25.68907097148424</v>
+        <v>18.10230499419437</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8766406629161367</v>
+        <v>1.034239343469995</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0476239477091845</v>
+        <v>0.0399927031155317</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1440</v>
+        <v>1232</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>414.8612657245436</v>
+        <v>231.1636457190954</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>13.3</v>
+        <v>143</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.29365498468978</v>
+        <v>30.72937857515684</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.11535594751786</v>
+        <v>23.20996608549361</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7205368078037757</v>
+        <v>1.230859198708374</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0278208911873492</v>
+        <v>-0.5994606080134155</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1213</v>
+        <v>1439</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>404.2085228280347</v>
+        <v>223.7675599585726</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>8.33</v>
+        <v>25.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.2941644744036</v>
+        <v>49.60016602858487</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.13904592345456</v>
+        <v>4.66953999105348</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8917145835558813</v>
+        <v>0.0225280276824404</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1023588984353297</v>
+        <v>-0.0071942910054995</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1517</v>
+        <v>1218</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>399.0930316102082</v>
+        <v>206.5916516356558</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10.5</v>
+        <v>17.9</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>54.06668945943703</v>
+        <v>30.98472265949025</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.81344643903937</v>
+        <v>28.37945090179172</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.912417240958982</v>
+        <v>0.8591651635655844</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0520074695204327</v>
+        <v>-0.1570264975334555</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1526</v>
+        <v>1471</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>399.0833221544994</v>
+        <v>197.4079620251212</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>14.55</v>
+        <v>10.95</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.04559711046511</v>
+        <v>48.24542337747956</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>22.13712446132882</v>
+        <v>14.45126524436638</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7684686686787151</v>
+        <v>1.235946107168569</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.040652897880984</v>
+        <v>0.0144767122112801</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1443</v>
+        <v>1309</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>391.9929205170098</v>
+        <v>194.395839303827</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>27.9</v>
+        <v>14.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>66.7508210942169</v>
+        <v>40.19815916056525</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.82969313868715</v>
+        <v>11.9217503575635</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4624922850753813</v>
+        <v>0.6817886332992179</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1352967946824557</v>
+        <v>-0.0296626664879235</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1464</v>
+        <v>1323</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>379.3508681419255</v>
+        <v>192.9425132487936</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10.3</v>
+        <v>19.8</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.42531546948776</v>
+        <v>46.81658869391678</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.90915778919362</v>
+        <v>14.42203888963332</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8630637326166987</v>
+        <v>0.9577574295683942</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0111766408135319</v>
+        <v>-0.0224389009582607</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1435</v>
+        <v>1109</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>377.3028185835054</v>
+        <v>188.1563542731412</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>14.1</v>
+        <v>14.65</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.01615144339371</v>
+        <v>43.18916699277757</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8.063136071575158</v>
+        <v>24.54063856724948</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.266370439663237</v>
+        <v>1.392091312012331</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1425275403388597</v>
+        <v>0.0261661743344631</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1527</v>
+        <v>1233</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>375.4010339967188</v>
+        <v>172.6575533082148</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.07420547307096</v>
+        <v>47.33900472060665</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.29289482011144</v>
+        <v>18.65928798531922</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6767657446985732</v>
+        <v>0.3374256644367731</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0043926283143771</v>
+        <v>0.06963801728022639</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1506</v>
+        <v>1220</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>375.3061570097166</v>
+        <v>171.9042477952381</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.41168372063035</v>
+        <v>38.38382357076729</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.52111867458808</v>
+        <v>30.30191371637733</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4686831307741343</v>
+        <v>0.5942116369070093</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0523609018830725</v>
+        <v>0.0183385446838285</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1217</v>
+        <v>1569</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>372.7572149681868</v>
+        <v>153.992834816581</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>55.28570957207075</v>
+        <v>41.03348304742002</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.27106263329659</v>
+        <v>14.1495462379899</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6520740971076495</v>
+        <v>0.5156235209366679</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0161309067016838</v>
+        <v>-0.0932497315529958</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1472</v>
+        <v>1410</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>370.4555137799081</v>
+        <v>131.0032214725879</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>91</v>
+        <v>24.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.40144167233694</v>
+        <v>34.2869672304565</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9.056578179387785</v>
+        <v>15.14909258404206</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3455513779908061</v>
+        <v>0.5409608012391172</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.4584873800473181</v>
+        <v>0.0231260323310376</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1530</v>
+        <v>1445</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>361.6070134371662</v>
+        <v>81.55552797341271</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>30.55</v>
+        <v>11</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.44762425357946</v>
+        <v>31.57245759113273</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>29.49427602684659</v>
+        <v>14.86745737527452</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2649638691575833</v>
+        <v>0.7572572916786937</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>1</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.4054164471075665</v>
+        <v>-0.0119745482591869</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1438</v>
+        <v>1325</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>357.1452006043351</v>
+        <v>81.2224697907068</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>22.25</v>
+        <v>26.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.60769420089458</v>
+        <v>43.9608806912912</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>28.8264731620782</v>
+        <v>12.8241025191739</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5971315524864168</v>
+        <v>0.6294322188050135</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,2182 +4598,9 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.4035812283249412</v>
+        <v>-0.0464958818346795</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>1203</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>味王</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>354.7451403976225</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>51.72744357064269</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>18.57749428547929</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>0.1922639248345938</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N79" s="2" t="n">
-        <v>0.0009775289035551999</v>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>聯華食</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>353.6995462514231</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>51.53770299363808</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>19.93705584123946</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>0.5567981918613102</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>0.1355616317184214</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>1454</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>台富</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>349.0736695870559</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>47.64023045079414</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>24.05118871567157</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>0.332869007896855</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>0.0064236140172303</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>1305</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>345.1881169569097</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>53.66545947211333</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>12.1099617320226</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>1.246338124289308</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>0.092627118227432</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>1340</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>勝悅-KY</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>338.8700335824805</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>51.03453311062326</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>16.84875228618575</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.5037596417152249</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>0.0336176425275572</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>1528</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>恩德</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>336.5183951742151</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>45.32050959426256</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>8.915214870525228</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>0.3880915368881186</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>-0.1907108160880026</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>1467</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>南緯</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>334.6507176597547</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>46.95046518961541</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>29.73270199406217</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0.577164341193007</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>-0.035580145999719</v>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>1219</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>福壽</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>334.5624817251229</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>42.89466189562577</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>28.89339861947294</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0.5429912998535098</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>0.031014080431561</v>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>1418</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>東華</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>330.2379994094288</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>49.26127743026068</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>24.40318894346667</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>0.3428776340162555</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-0.0046080205085807</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>1108</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>幸福</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>329.2598410072911</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>49.84830139789614</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>31.89090345430081</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0.3593337663392648</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>0.052998925489842</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>1512</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>瑞利</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>326.0500249839791</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>58.46872544684311</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>10.96966951410226</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>1.416511479762644</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>0.0426032847462061</v>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>1324</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>地球</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>312.5690281201718</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>46.67001983775374</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>22.64983927564736</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>2.047306422170674</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>0.0124484818087332</v>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>1470</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>大統新創</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>311.7085454462015</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>35.30734962947267</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>12.74841716738727</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0.0056849451765659</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-1.438726190395205</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>1316</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>上曜</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>311.612045199291</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>52.06757724934013</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>20.39008776163514</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>0.6861769947223996</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>0.101038116706495</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>1516</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>川飛</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>307.4564520343147</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>43.99715183782658</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>15.89886142518246</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0.5621324648423434</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>-0.0739357179128407</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>1529</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>樂事綠能</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>291.491074206124</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>52.38935809628039</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>18.58350321730451</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>0.5801214237898505</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>0.0507438717363569</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>1582</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>信錦</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>283.1826076335977</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>44.24367230531747</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>21.87882572903472</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0.3471153347949783</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>-1.839261504536931</v>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>1522</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>堤維西</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>281.6444765222221</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>54.41192127909954</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>16.884223158752</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0.7004570992660725</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>0.0685819936162286</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>278.528638241205</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>31.35571844374053</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>42.54680098601817</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>0.6249992823161552</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>0.111636434297841</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>1441</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>大東</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>257.3797088412625</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>43.41937497839606</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>15.39298727831139</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0.2197384500476081</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>0.0199911622907344</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>1417</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>嘉裕</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>252.86159507928</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>53.64188323962764</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>18.10230499419437</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>1.034239343469995</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>0.0399927031155317</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>1459</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>聯發</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>250.186030754045</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>52.85089422884813</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>15.61608054271682</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0.1962857796854811</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0.0195901217367808</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>1232</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>大統益</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>231.1636457190954</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>30.72937857515684</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>23.20996608549361</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>1.230859198708374</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-0.5994606080134155</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>1439</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>雋揚</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>223.7675599585726</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>49.60016602858487</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>4.66953999105348</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>0.0225280276824404</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-0.0071942910054995</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>1463</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>強盛新</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>218.0984508592308</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>41.98724611543204</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>10.67165676068855</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>0.9686308257880925</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>0.001250854821777</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>1218</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>泰山</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>206.5916516356558</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>30.98472265949025</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>28.37945090179172</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0.8591651635655844</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>-0.1570264975334555</v>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>1473</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>台南</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>200.4286929516823</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>38.30558541494312</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>20.75580764590497</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>0.9254436722074634</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-0.0092111950266381</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>1519</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>197.695441498276</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>833</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>49.81773353165728</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>11.80543860474762</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0.8292367848057336</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>-2.605913246909886</v>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>1471</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>首利</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>197.4079620251212</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>48.24542337747956</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>14.45126524436638</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>1.235946107168569</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>0.0144767122112801</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>1309</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>194.395839303827</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>40.19815916056525</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>11.9217503575635</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0.6817886332992179</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>-0.0296626664879235</v>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>1323</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>永裕</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>192.9425132487936</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>46.81658869391678</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>14.42203888963332</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>0.9577574295683942</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>-0.0224389009582607</v>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>1109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>信大</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>188.1563542731412</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>43.18916699277757</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>24.54063856724948</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>1.392091312012331</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>0.0261661743344631</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>1233</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>天仁</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>172.6575533082148</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>47.33900472060665</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>18.65928798531922</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>0.3374256644367731</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>0.06963801728022639</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>1457</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>宜進</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>172.1553085539658</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>45.512055394927</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>19.99132615262341</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>0.8348609736415091</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>-0.0147298748087928</v>
-      </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>1220</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>台榮</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>171.9042477952381</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>38.38382357076729</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>30.30191371637733</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>0.5942116369070093</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>0.0183385446838285</v>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>1451</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>年興</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>171.6909591493734</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>49.31627723615088</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>11.17032851585702</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0.5584919651855531</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>0.0453369316386756</v>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>1468</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>昶和</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>159.8703921308577</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>49.48317207004429</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>9.356195427416788</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>1.332329260188842</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>0.0149295173073751</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>1569</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>濱川</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>153.992834816581</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>41.03348304742002</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>14.1495462379899</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>0.5156235209366679</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>-0.0932497315529958</v>
-      </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>1410</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>南染</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>131.0032214725879</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>34.2869672304565</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>15.14909258404206</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0.5409608012391172</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>0.0231260323310376</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>1445</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>大宇</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>81.55552797341271</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>31.57245759113273</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>14.86745737527452</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0.7572572916786937</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>-0.0119745482591869</v>
-      </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>1325</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>恆大</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>81.2224697907068</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>43.9608806912912</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>12.8241025191739</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>0.6294322188050135</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-0.0464958818346795</v>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq1_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1210</v>
+        <v>1568</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>854.5497812820505</v>
+        <v>916.0272276098456</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.7</v>
+        <v>46.05</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.00850916201571</v>
+        <v>64.93780717246926</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28.29750800717133</v>
+        <v>45.83260835280667</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5941407308952612</v>
+        <v>2.229706187786221</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1376317583020645</v>
+        <v>-0.2365567621796294</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1342</v>
+        <v>1563</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>815.7538899352642</v>
+        <v>915.6222295637924</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116</v>
+        <v>67.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>72.52214129145692</v>
+        <v>65.13214971034338</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>41.98778044201702</v>
+        <v>45.13927444171792</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9947541827124956</v>
+        <v>2.274472021495549</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.485242999900608</v>
+        <v>-0.3015448540281076</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1307</v>
+        <v>1503</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>802.2601313372636</v>
+        <v>892.7061157387524</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36.4</v>
+        <v>241.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.82540943480555</v>
+        <v>61.61356524461225</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.89402956076432</v>
+        <v>21.42477104101332</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5260131337263608</v>
+        <v>0.8997420603596417</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2988626560117808</v>
+        <v>0.0577965948213785</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1236</v>
+        <v>1455</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>797.8456021055274</v>
+        <v>863.8000379800418</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>25.8</v>
+        <v>10.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.21876149397025</v>
+        <v>73.07598197540156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.97363160233272</v>
+        <v>43.02226714854736</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.05312651146466</v>
+        <v>2.197635395191481</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1159850736446855</v>
+        <v>0.0671395500903484</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1436</v>
+        <v>1210</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>748.7050098124354</v>
+        <v>854.5497812820505</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>47.5</v>
+        <v>54.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.5234829461923</v>
+        <v>56.00850916201571</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.5980696850501</v>
+        <v>28.29750800717133</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.682746045526478</v>
+        <v>0.5941407308952612</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4113201450827294</v>
+        <v>0.1376317583020645</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1304</v>
+        <v>1342</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>736.3122637934827</v>
+        <v>815.7538899352642</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.55</v>
+        <v>116</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.82189578120946</v>
+        <v>72.52214129145692</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.43802983977482</v>
+        <v>41.98778044201702</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.36337126941053</v>
+        <v>0.9947541827124956</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.08904455322678299</v>
+        <v>1.485242999900608</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1339</v>
+        <v>1513</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>726.242673475292</v>
+        <v>803.4700676590958</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>43.95</v>
+        <v>176.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.03984517232819</v>
+        <v>61.67521166497431</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.37716800699772</v>
+        <v>21.14224504369142</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7716085142239336</v>
+        <v>0.8880220477980655</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0266077430382258</v>
+        <v>-0.1196359775771456</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1432</v>
+        <v>1307</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>725.0816647553238</v>
+        <v>802.2601313372636</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17.6</v>
+        <v>36.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.1443518782105</v>
+        <v>68.82540943480555</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.35439014996757</v>
+        <v>30.89402956076432</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.153957115632234</v>
+        <v>0.5260131337263608</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.06502627600529511</v>
+        <v>0.2988626560117808</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1313</v>
+        <v>1236</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>699.5396528141365</v>
+        <v>797.8456021055274</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.6</v>
+        <v>25.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.40777970188018</v>
+        <v>63.21876149397025</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>19.53659650926148</v>
+        <v>14.97363160233272</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.047899710641487</v>
+        <v>3.05312651146466</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.07192872993325421</v>
+        <v>0.1159850736446855</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>692.8838996269352</v>
+        <v>748.7050098124354</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16.95</v>
+        <v>47.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.99272823920637</v>
+        <v>55.5234829461923</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.92622368880813</v>
+        <v>29.5980696850501</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.920412451593225</v>
+        <v>1.682746045526478</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1077369110086075</v>
+        <v>0.4113201450827294</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1338</v>
+        <v>1304</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>686.0157226220391</v>
+        <v>736.3122637934827</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17.2</v>
+        <v>13.55</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.37026794230912</v>
+        <v>56.82189578120946</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.52508560192718</v>
+        <v>17.43802983977482</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2960259134605936</v>
+        <v>1.36337126941053</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>5</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0667006189894196</v>
+        <v>0.08904455322678299</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>678.3656810588507</v>
+        <v>726.242673475292</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32.15</v>
+        <v>43.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>68.33980308725089</v>
+        <v>55.03984517232819</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44.5098725515812</v>
+        <v>25.37716800699772</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.440236062360517</v>
+        <v>0.7716085142239336</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3848319477861786</v>
+        <v>-0.0266077430382258</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>676.5070199521294</v>
+        <v>725.0816647553238</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>28.85</v>
+        <v>17.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.03970351754613</v>
+        <v>66.1443518782105</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18.29242953046834</v>
+        <v>22.35439014996757</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5014713294127671</v>
+        <v>2.153957115632234</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2309345337692722</v>
+        <v>0.06502627600529511</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1319</v>
+        <v>1456</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>659.6088013199532</v>
+        <v>723.5060746387871</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99.2</v>
+        <v>15.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.42020484759104</v>
+        <v>71.73396626291438</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.27035655853308</v>
+        <v>21.70634066446499</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.252047492523111</v>
+        <v>1.45060746387871</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.09856468346116461</v>
+        <v>0.2194367130684937</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1444</v>
+        <v>1560</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>657.5542567724973</v>
+        <v>711.3956194962132</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7.04</v>
+        <v>700</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.84261111634376</v>
+        <v>56.54323349816397</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33.4810933077659</v>
+        <v>23.07441877788924</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4787007153984733</v>
+        <v>0.5320029401901213</v>
       </c>
       <c r="K19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0153050651076618</v>
+        <v>-4.647935620920336</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1102</v>
+        <v>1313</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>652.8802183208379</v>
+        <v>699.5396528141365</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.8</v>
+        <v>11.6</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>63.25795357631394</v>
+        <v>59.40777970188018</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16.24054038084162</v>
+        <v>19.53659650926148</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7292745764137463</v>
+        <v>1.047899710641487</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2460159324520993</v>
+        <v>0.07192872993325421</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1310</v>
+        <v>1515</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>649.2035235197391</v>
+        <v>699.3100456859476</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9.26</v>
+        <v>25.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.10062592635524</v>
+        <v>64.43587110969604</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.17743653583982</v>
+        <v>23.7993265557867</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.376397343442056</v>
+        <v>2.031004568594761</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0876633298989556</v>
+        <v>0.2364530078577263</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1216</v>
+        <v>1434</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>647.4525091711652</v>
+        <v>692.8838996269352</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>74.5</v>
+        <v>16.95</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.14904454895826</v>
+        <v>65.99272823920637</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.76337920467265</v>
+        <v>25.92622368880813</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.569797742192853</v>
+        <v>0.920412451593225</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1498669317323347</v>
+        <v>0.1077369110086075</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1419</v>
+        <v>1338</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>640.7799540690776</v>
+        <v>686.0157226220391</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.42886703956965</v>
+        <v>60.37026794230912</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.54105185696687</v>
+        <v>21.52508560192718</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4701577426923286</v>
+        <v>0.2960259134605936</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.117014034272866</v>
+        <v>0.0667006189894196</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1409</v>
+        <v>1321</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>624.8202770200872</v>
+        <v>678.3656810588507</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>25.6</v>
+        <v>32.15</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.86688740500579</v>
+        <v>68.33980308725089</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>33.90228862072883</v>
+        <v>44.5098725515812</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.645819034232483</v>
+        <v>1.440236062360517</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0691676826753822</v>
+        <v>0.3848319477861786</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1312</v>
+        <v>1402</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>620.3260340202017</v>
+        <v>676.5070199521294</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13.5</v>
+        <v>28.85</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.90061377914206</v>
+        <v>63.03970351754613</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>30.0566255908111</v>
+        <v>18.29242953046834</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5972918402774777</v>
+        <v>0.5014713294127671</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0500154251928375</v>
+        <v>0.2309345337692722</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1227</v>
+        <v>1533</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>612.2643517411922</v>
+        <v>674.5110239426173</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>29.1</v>
+        <v>38.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.73017837542036</v>
+        <v>54.66709620701491</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.7680127063311</v>
+        <v>49.05853769936262</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9092581356694578</v>
+        <v>0.3306317089805499</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1147458914991183</v>
+        <v>-0.3217233625010298</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1225</v>
+        <v>1319</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>609.5081289041721</v>
+        <v>659.6088013199532</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>32.25</v>
+        <v>99.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.15724440147043</v>
+        <v>57.42020484759104</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.48631186884588</v>
+        <v>36.27035655853308</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7508128904172097</v>
+        <v>1.252047492523111</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4051218759914243</v>
+        <v>0.09856468346116461</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>605.9669472862163</v>
+        <v>657.5542567724973</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>16.7</v>
+        <v>7.04</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>60.10552185122149</v>
+        <v>58.84261111634376</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.75096354072749</v>
+        <v>33.4810933077659</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7044634451767535</v>
+        <v>0.4787007153984733</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0408561489174495</v>
+        <v>0.0153050651076618</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>584.5331908379574</v>
+        <v>652.8802183208379</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.1</v>
+        <v>35.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>62.09469360791442</v>
+        <v>63.25795357631394</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.08434188280217</v>
+        <v>16.24054038084162</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.673098637683775</v>
+        <v>0.7292745764137463</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.077195968919125</v>
+        <v>0.2460159324520993</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>580.2895479050012</v>
+        <v>649.2035235197391</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7.78</v>
+        <v>9.26</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.23069085151434</v>
+        <v>60.10062592635524</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.09222657468816</v>
+        <v>20.17743653583982</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6112692406684329</v>
+        <v>2.376397343442056</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0040936721384182</v>
+        <v>0.0876633298989556</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1101</v>
+        <v>1216</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>573.4302563936706</v>
+        <v>647.4525091711652</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>24.5</v>
+        <v>74.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.76456283138577</v>
+        <v>53.14904454895826</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.91001708951427</v>
+        <v>20.76337920467265</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9638060972957572</v>
+        <v>1.569797742192853</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0472354811198828</v>
+        <v>0.1498669317323347</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1308</v>
+        <v>1532</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>559.6601571998519</v>
+        <v>644.8475551936692</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>13.95</v>
+        <v>24</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.64491994868592</v>
+        <v>72.49973663597416</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.73111346876891</v>
+        <v>40.63110816026887</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.131505124513402</v>
+        <v>1.179435935390436</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0881924123875675</v>
+        <v>0.2323397004517088</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>549.8241619591524</v>
+        <v>640.7799540690776</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>17.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>64.79735522798596</v>
+        <v>57.42886703956965</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.69874319390791</v>
+        <v>21.54105185696687</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3910277401585884</v>
+        <v>0.4701577426923286</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1932562636720068</v>
+        <v>0.117014034272866</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1110</v>
+        <v>1409</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>547.9092829079705</v>
+        <v>624.8202770200872</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15.55</v>
+        <v>25.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.18459198908</v>
+        <v>58.86688740500579</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.88317198925517</v>
+        <v>33.90228862072883</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6772333045779196</v>
+        <v>1.645819034232483</v>
       </c>
       <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0629090938443119</v>
+        <v>-0.0691676826753822</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1442</v>
+        <v>1312</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>523.9317216144625</v>
+        <v>620.3260340202017</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.30938267660233</v>
+        <v>58.90061377914206</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.4077746077942</v>
+        <v>30.0566255908111</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8837519370650183</v>
+        <v>0.5972918402774777</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.138259192702071</v>
+        <v>0.0500154251928375</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1229</v>
+        <v>1475</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>514.4295924979665</v>
+        <v>618.7254215845575</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>41.9</v>
+        <v>27.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.04519475643837</v>
+        <v>61.00758688017953</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.35375012840548</v>
+        <v>22.6007751814056</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.947929693493524</v>
+        <v>0.992961267887884</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1214437077844433</v>
+        <v>0.2629530789050555</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1423</v>
+        <v>1227</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>507.9161411936741</v>
+        <v>612.2643517411922</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>39.65</v>
+        <v>29.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>33.13793386110925</v>
+        <v>56.73017837542036</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>28.26850913452445</v>
+        <v>18.7680127063311</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3916141193674077</v>
+        <v>0.9092581356694578</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.208042610545323</v>
+        <v>0.1147458914991183</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1437</v>
+        <v>1225</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>497.3689029848045</v>
+        <v>609.5081289041721</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>29.55</v>
+        <v>32.25</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>59.95079616603009</v>
+        <v>59.15724440147043</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26.13949434108144</v>
+        <v>21.48631186884588</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6376628249354505</v>
+        <v>0.7508128904172097</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1481435158737044</v>
+        <v>0.4051218759914243</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1341</v>
+        <v>1446</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>493.3586738736569</v>
+        <v>605.9669472862163</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>62</v>
+        <v>16.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.2657116364898</v>
+        <v>60.10552185122149</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10.99946568005531</v>
+        <v>26.75096354072749</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.878707329473994</v>
+        <v>0.7044634451767535</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.09921629813862599</v>
+        <v>0.0408561489174495</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1416</v>
+        <v>1525</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>475.6627656593615</v>
+        <v>591.5406374380354</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11.1</v>
+        <v>66</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45.29208674086332</v>
+        <v>51.98658037841993</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.09270747016262</v>
+        <v>27.27099740091602</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8693758241844532</v>
+        <v>0.2254912162044985</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.018574430725019</v>
+        <v>-0.4187585458299818</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>446.1247328722617</v>
+        <v>584.5331908379574</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>13.8</v>
+        <v>29.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.45660706279585</v>
+        <v>62.09469360791442</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.94351070208299</v>
+        <v>31.08434188280217</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5997460309275028</v>
+        <v>1.673098637683775</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0553515385723448</v>
+        <v>0.077195968919125</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1413</v>
+        <v>1314</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>431.3410897264375</v>
+        <v>580.2895479050012</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>9.44</v>
+        <v>7.78</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.51334067808513</v>
+        <v>55.23069085151434</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6.614917610038835</v>
+        <v>15.09222657468816</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.9296723653964544</v>
+        <v>0.6112692406684329</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0112643344896217</v>
+        <v>0.0040936721384182</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1256</v>
+        <v>1101</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>431.3045291912051</v>
+        <v>573.4302563936706</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>181.5</v>
+        <v>24.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.24491147580878</v>
+        <v>51.76456283138577</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.89612076945481</v>
+        <v>14.91001708951427</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6831323681025595</v>
+        <v>0.9638060972957572</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.208574045349883</v>
+        <v>0.0472354811198828</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1315</v>
+        <v>1531</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>421.7182022320778</v>
+        <v>573.3665503321564</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>62.3</v>
+        <v>12.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.62021652055941</v>
+        <v>54.89292335686327</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12.72777089981604</v>
+        <v>19.06976099665065</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3.065663976084421</v>
+        <v>0.3336761861622408</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1099375537097131</v>
+        <v>0.0383537570905944</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1201</v>
+        <v>1477</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>415.1313572441856</v>
+        <v>571.5466910334386</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12.55</v>
+        <v>221.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>55.59154997664239</v>
+        <v>49.31852108141658</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.68907097148424</v>
+        <v>23.21489132688848</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8766406629161367</v>
+        <v>1.652671112942963</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0476239477091845</v>
+        <v>-0.2581856510711137</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1440</v>
+        <v>1308</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>414.8612657245436</v>
+        <v>559.6601571998519</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.3</v>
+        <v>13.95</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.29365498468978</v>
+        <v>53.64491994868592</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.11535594751786</v>
+        <v>14.73111346876891</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7205368078037757</v>
+        <v>1.131505124513402</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0278208911873492</v>
+        <v>0.0881924123875675</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1213</v>
+        <v>1414</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>404.2085228280347</v>
+        <v>549.8241619591524</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>8.33</v>
+        <v>17.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.2941644744036</v>
+        <v>64.79735522798596</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.13904592345456</v>
+        <v>25.69874319390791</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8917145835558813</v>
+        <v>0.3910277401585884</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1023588984353297</v>
+        <v>0.1932562636720068</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1443</v>
+        <v>1476</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>391.9929205170098</v>
+        <v>549.0748523148882</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>27.9</v>
+        <v>327</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>66.7508210942169</v>
+        <v>40.66196375066807</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.82969313868715</v>
+        <v>13.78585032809397</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4624922850753813</v>
+        <v>1.427371551081816</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1352967946824557</v>
+        <v>-2.400246122748035</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1435</v>
+        <v>1110</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>377.3028185835054</v>
+        <v>547.9092829079705</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14.1</v>
+        <v>15.55</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.01615144339371</v>
+        <v>57.18459198908</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>8.063136071575158</v>
+        <v>32.88317198925517</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.266370439663237</v>
+        <v>0.6772333045779196</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1425275403388597</v>
+        <v>0.0629090938443119</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1217</v>
+        <v>1514</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>372.7572149681868</v>
+        <v>547.0340572788253</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>121.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.28570957207075</v>
+        <v>48.9598732746133</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.27106263329659</v>
+        <v>23.34844941935013</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6520740971076495</v>
+        <v>0.3473575093056278</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0161309067016838</v>
+        <v>-1.30619983612317</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1438</v>
+        <v>1465</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>357.1452006043351</v>
+        <v>540.8765755558298</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>22.25</v>
+        <v>12.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.60769420089458</v>
+        <v>57.66207980402617</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.8264731620782</v>
+        <v>14.39883835428248</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5971315524864168</v>
+        <v>0.4828718709459609</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4035812283249412</v>
+        <v>0.0102360332756602</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1203</v>
+        <v>1453</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>354.7451403976225</v>
+        <v>531.988111470459</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>43</v>
+        <v>11.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.72744357064269</v>
+        <v>56.93735087282981</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.57749428547929</v>
+        <v>27.90554225387556</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1922639248345938</v>
+        <v>0.4988111470458976</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0009775289035551999</v>
+        <v>0.07786396424651019</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1231</v>
+        <v>1442</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>353.6995462514231</v>
+        <v>523.9317216144625</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>28</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.53770299363808</v>
+        <v>57.30938267660233</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.93705584123946</v>
+        <v>21.4077746077942</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5567981918613102</v>
+        <v>0.8837519370650183</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1355616317184214</v>
+        <v>0.138259192702071</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1305</v>
+        <v>1229</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>345.1881169569097</v>
+        <v>514.4295924979665</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>13.25</v>
+        <v>41.9</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.66545947211333</v>
+        <v>54.04519475643837</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.1099617320226</v>
+        <v>25.35375012840548</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.246338124289308</v>
+        <v>0.947929693493524</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.092627118227432</v>
+        <v>0.1214437077844433</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1340</v>
+        <v>1504</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>338.8700335824805</v>
+        <v>512.1720945122786</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>5.72</v>
+        <v>70</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.03453311062326</v>
+        <v>47.16487611591501</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.84875228618575</v>
+        <v>21.95656548367733</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5037596417152249</v>
+        <v>0.4153806981740384</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0336176425275572</v>
+        <v>-0.9550825539175456</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1219</v>
+        <v>1423</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>334.5624817251229</v>
+        <v>507.9161411936741</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>12.6</v>
+        <v>39.65</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>42.89466189562577</v>
+        <v>33.13793386110925</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>28.89339861947294</v>
+        <v>28.26850913452445</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5429912998535098</v>
+        <v>0.3916141193674077</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.031014080431561</v>
+        <v>-0.208042610545323</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1418</v>
+        <v>1474</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>330.2379994094288</v>
+        <v>504.2037480061646</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>18.5</v>
+        <v>10.25</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.26127743026068</v>
+        <v>55.23164134041306</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>24.40318894346667</v>
+        <v>28.31508080088525</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3428776340162555</v>
+        <v>0.4714339473541764</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0046080205085807</v>
+        <v>0.0045903981878263</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1108</v>
+        <v>1452</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>329.2598410072911</v>
+        <v>499.3486648378032</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>13.9</v>
+        <v>11.15</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.84830139789614</v>
+        <v>59.7412031442096</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>31.89090345430081</v>
+        <v>18.95128833939903</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3593337663392648</v>
+        <v>1.542091811107839</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.052998925489842</v>
+        <v>0.0655651425900125</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1324</v>
+        <v>1437</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>312.5690281201718</v>
+        <v>497.3689029848045</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10.4</v>
+        <v>29.55</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.67001983775374</v>
+        <v>59.95079616603009</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.64983927564736</v>
+        <v>26.13949434108144</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.047306422170674</v>
+        <v>0.6376628249354505</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0124484818087332</v>
+        <v>0.1481435158737044</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1316</v>
+        <v>1524</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>311.612045199291</v>
+        <v>494.8344686507933</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10.95</v>
+        <v>29.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.06757724934013</v>
+        <v>48.07306704454277</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.39008776163514</v>
+        <v>16.23460065039131</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6861769947223996</v>
+        <v>0.2846319322292868</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.101038116706495</v>
+        <v>-0.2908696764008172</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1529</v>
+        <v>1341</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>291.491074206124</v>
+        <v>493.3586738736569</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>22.9</v>
+        <v>62</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.38935809628039</v>
+        <v>50.2657116364898</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.58350321730451</v>
+        <v>10.99946568005531</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5801214237898505</v>
+        <v>1.878707329473994</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0507438717363569</v>
+        <v>-0.09921629813862599</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1582</v>
+        <v>1537</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>283.1826076335977</v>
+        <v>489.9209484337617</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>93.8</v>
+        <v>127.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.24367230531747</v>
+        <v>58.73620522353673</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.87882572903472</v>
+        <v>9.951057440364451</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3471153347949783</v>
+        <v>0.6057946502716004</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.839261504536931</v>
+        <v>-0.0147820585104838</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1215</v>
+        <v>1416</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>278.528638241205</v>
+        <v>475.6627656593615</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>115</v>
+        <v>11.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>31.35571844374053</v>
+        <v>45.29208674086332</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>42.54680098601817</v>
+        <v>25.09270747016262</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6249992823161552</v>
+        <v>0.8693758241844532</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.111636434297841</v>
+        <v>-0.018574430725019</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>257.3797088412625</v>
+        <v>471.3314279793832</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>9.25</v>
+        <v>6.03</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.41937497839606</v>
+        <v>50.18861129696867</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.39298727831139</v>
+        <v>31.17090116562068</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2197384500476081</v>
+        <v>0.5323135605998941</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0199911622907344</v>
+        <v>-0.0802919177022139</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1417</v>
+        <v>1460</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>252.86159507928</v>
+        <v>447.9664600540518</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>8.52</v>
+        <v>7.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.64188323962764</v>
+        <v>53.89257654767219</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.10230499419437</v>
+        <v>14.6321740255548</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.034239343469995</v>
+        <v>0.7173800024503196</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0399927031155317</v>
+        <v>0.0064840725158421</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1232</v>
+        <v>1103</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>231.1636457190954</v>
+        <v>446.1247328722617</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>143</v>
+        <v>13.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>30.72937857515684</v>
+        <v>62.45660706279585</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.20996608549361</v>
+        <v>15.94351070208299</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.230859198708374</v>
+        <v>0.5997460309275028</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5994606080134155</v>
+        <v>0.0553515385723448</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1439</v>
+        <v>1466</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>223.7675599585726</v>
+        <v>445.4267459812485</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>25.3</v>
+        <v>14.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.60016602858487</v>
+        <v>44.71235943981799</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4.66953999105348</v>
+        <v>17.20957073376873</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.0225280276824404</v>
+        <v>2.342674598124848</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0071942910054995</v>
+        <v>0.0575697905047059</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1218</v>
+        <v>1413</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>206.5916516356558</v>
+        <v>431.3410897264375</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.9</v>
+        <v>9.44</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>30.98472265949025</v>
+        <v>49.51334067808513</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>28.37945090179172</v>
+        <v>6.614917610038835</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8591651635655844</v>
+        <v>0.9296723653964544</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1570264975334555</v>
+        <v>-0.0112643344896217</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1471</v>
+        <v>1256</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>197.4079620251212</v>
+        <v>431.3045291912051</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>10.95</v>
+        <v>181.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>48.24542337747956</v>
+        <v>49.24491147580878</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.45126524436638</v>
+        <v>21.89612076945481</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.235946107168569</v>
+        <v>0.6831323681025595</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0144767122112801</v>
+        <v>-2.208574045349883</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>194.395839303827</v>
+        <v>421.7182022320778</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>14.75</v>
+        <v>62.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>40.19815916056525</v>
+        <v>56.62021652055941</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.9217503575635</v>
+        <v>12.72777089981604</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6817886332992179</v>
+        <v>3.065663976084421</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0296626664879235</v>
+        <v>0.1099375537097131</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1323</v>
+        <v>1521</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>192.9425132487936</v>
+        <v>417.3278842801328</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>19.8</v>
+        <v>26.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.81658869391678</v>
+        <v>54.29160453195838</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.42203888963332</v>
+        <v>19.91299463666361</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9577574295683942</v>
+        <v>0.5573735497188963</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0224389009582607</v>
+        <v>-0.0937303265192638</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1109</v>
+        <v>1201</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>188.1563542731412</v>
+        <v>415.1313572441856</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>14.65</v>
+        <v>12.55</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.18916699277757</v>
+        <v>55.59154997664239</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24.54063856724948</v>
+        <v>25.68907097148424</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.392091312012331</v>
+        <v>0.8766406629161367</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0261661743344631</v>
+        <v>0.0476239477091845</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1233</v>
+        <v>1440</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>172.6575533082148</v>
+        <v>414.8612657245436</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>28</v>
+        <v>13.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.33900472060665</v>
+        <v>53.29365498468978</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.65928798531922</v>
+        <v>23.11535594751786</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3374256644367731</v>
+        <v>0.7205368078037757</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.06963801728022639</v>
+        <v>-0.0278208911873492</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>171.9042477952381</v>
+        <v>404.2085228280347</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11.7</v>
+        <v>8.33</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>38.38382357076729</v>
+        <v>51.2941644744036</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.30191371637733</v>
+        <v>11.13904592345456</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5942116369070093</v>
+        <v>0.8917145835558813</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0183385446838285</v>
+        <v>0.1023588984353297</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1569</v>
+        <v>1535</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>153.992834816581</v>
+        <v>404.1937756948049</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.7</v>
+        <v>50.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.03348304742002</v>
+        <v>52.72623697913821</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.1495462379899</v>
+        <v>24.88772596445248</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5156235209366679</v>
+        <v>0.7315098003191723</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0932497315529958</v>
+        <v>0.0805316343491376</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1410</v>
+        <v>1517</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>131.0032214725879</v>
+        <v>399.0930316102082</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>24.85</v>
+        <v>10.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>34.2869672304565</v>
+        <v>54.06668945943703</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.14909258404206</v>
+        <v>21.81344643903937</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5409608012391172</v>
+        <v>0.912417240958982</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0231260323310376</v>
+        <v>0.0520074695204327</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1445</v>
+        <v>1526</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>81.55552797341271</v>
+        <v>399.0833221544994</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11</v>
+        <v>14.55</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>31.57245759113273</v>
+        <v>43.04559711046511</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.86745737527452</v>
+        <v>22.13712446132882</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7572572916786937</v>
+        <v>0.7684686686787151</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,62 +4545,2977 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0119745482591869</v>
+        <v>0.040652897880984</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>立益</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>391.9929205170098</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>66.7508210942169</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>18.82969313868715</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.4624922850753813</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0.1352967946824557</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>中福</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>377.3028185835054</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>52.01615144339371</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>8.063136071575158</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1.266370439663237</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0.1425275403388597</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>鑽全</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>375.4010339967188</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>55.07420547307096</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>18.29289482011144</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.6767657446985732</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-0.0043926283143771</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>正道</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>375.3061570097166</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>48.41168372063035</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>26.52111867458808</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.4686831307741343</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.0523609018830725</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>愛之味</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>372.7572149681868</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>55.28570957207075</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>22.27106263329659</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.6520740971076495</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.0161309067016838</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>三洋實業</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>370.4555137799081</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>52.40144167233694</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>9.056578179387785</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.3455513779908061</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.4584873800473181</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>亞崴</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>361.6070134371662</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>50.44762425357946</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>29.49427602684659</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.2649638691575833</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.4054164471075665</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>得力</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>359.3508681419254</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>49.42531546948776</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>21.90915778919362</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.8630637326166987</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-0.0111766408135319</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>357.1452006043351</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>52.60769420089458</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>28.8264731620782</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.5971315524864168</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.4035812283249412</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>味王</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>354.7451403976225</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>51.72744357064269</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>18.57749428547929</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.1922639248345938</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.0009775289035551999</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>聯華食</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>353.6995462514231</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>51.53770299363808</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>19.93705584123946</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.5567981918613102</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.1355616317184214</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>台富</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>349.0736695870559</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>47.64023045079414</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>24.05118871567157</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.332869007896855</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.0064236140172303</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>華夏</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>345.1881169569097</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>53.66545947211333</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>12.1099617320226</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1.246338124289308</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.092627118227432</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>勝悅-KY</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>338.8700335824805</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>51.03453311062326</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>16.84875228618575</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.5037596417152249</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.0336176425275572</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>恩德</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>336.5183951742151</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>45.32050959426256</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>8.915214870525228</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.3880915368881186</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.1907108160880026</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>南緯</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>334.6507176597547</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>46.95046518961541</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>29.73270199406217</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.577164341193007</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.035580145999719</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>福壽</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>334.5624817251229</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>42.89466189562577</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>28.89339861947294</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.5429912998535098</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.031014080431561</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>東華</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>330.2379994094288</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>49.26127743026068</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>24.40318894346667</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.3428776340162555</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.0046080205085807</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>幸福</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>329.2598410072911</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>49.84830139789614</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>31.89090345430081</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.3593337663392648</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0.052998925489842</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>瑞利</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>326.0500249839791</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>58.46872544684311</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>10.96966951410226</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.416511479762644</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.0426032847462061</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>312.5690281201718</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>46.67001983775374</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>22.64983927564736</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.047306422170674</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.0124484818087332</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>大統新創</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>311.7085454462015</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>35.30734962947267</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>12.74841716738727</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.0056849451765659</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-1.438726190395205</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>上曜</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>311.612045199291</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>52.06757724934013</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>20.39008776163514</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.6861769947223996</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.101038116706495</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>川飛</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>307.4564520343147</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>43.99715183782658</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>15.89886142518246</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.5621324648423434</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.0739357179128407</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>喬福</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>305.4431066212883</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>51.74829250728028</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>15.93150403556239</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.5763318913027298</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.0244850623306377</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>樂事綠能</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>291.491074206124</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>52.38935809628039</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>18.58350321730451</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.5801214237898505</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>0.0507438717363569</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>信錦</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>283.1826076335977</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>44.24367230531747</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>21.87882572903472</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.3471153347949783</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-1.839261504536931</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>堤維西</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>281.6444765222221</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>54.41192127909954</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>16.884223158752</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.7004570992660725</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.0685819936162286</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>278.528638241205</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>31.35571844374053</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>42.54680098601817</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.6249992823161552</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0.111636434297841</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>伸興</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>271.9423747476848</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>54.08258857966145</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>12.47863259188737</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.8615121072072233</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.0872922283522022</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>和大</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>269.306343011183</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>42.98321828378464</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>14.38260356438203</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.4394219457263302</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.1728504943945374</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>正峰</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>266.4550499594624</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>37.94587831173669</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>6.441273890804566</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.0933335741941699</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.5293624812077768</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>大東</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>257.3797088412625</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>43.41937497839606</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>15.39298727831139</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.2197384500476081</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.0199911622907344</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>嘉裕</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>252.86159507928</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>53.64188323962764</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>18.10230499419437</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1.034239343469995</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.0399927031155317</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>聯發</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>250.186030754045</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>52.85089422884813</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>15.61608054271682</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.1962857796854811</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.0195901217367808</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>巨庭</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>245.9704695083771</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>45.20967880056392</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>18.27485936514641</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.5764937850685035</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.0366568057867585</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>大統益</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>231.1636457190954</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30.72937857515684</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>23.20996608549361</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.230859198708374</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.5994606080134155</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>雋揚</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>223.7675599585726</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>49.60016602858487</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>4.66953999105348</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.0225280276824404</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0071942910054995</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>強盛新</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>218.0984508592308</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>41.98724611543204</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>10.67165676068855</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.9686308257880925</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.001250854821777</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>泰山</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>206.5916516356558</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30.98472265949025</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>28.37945090179172</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.8591651635655844</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.1570264975334555</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>200.4286929516823</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>38.30558541494312</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>20.75580764590497</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.9254436722074634</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.0092111950266381</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>197.695441498276</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>49.81773353165728</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>11.80543860474762</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.8292367848057336</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-2.605913246909886</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>首利</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>197.4079620251212</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>48.24542337747956</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>14.45126524436638</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>1.235946107168569</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0.0144767122112801</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>台達化</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>194.395839303827</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>40.19815916056525</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>11.9217503575635</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.6817886332992179</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.0296626664879235</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>永裕</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>192.9425132487936</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>46.81658869391678</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>14.42203888963332</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.9577574295683942</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.0224389009582607</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>信大</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>188.1563542731412</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>43.18916699277757</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>24.54063856724948</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.392091312012331</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.0261661743344631</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>錩泰</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>179.9019545869859</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>52.79166440016566</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>13.15554848381841</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.3772725183801061</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.1845861304210637</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>天仁</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>172.6575533082148</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>47.33900472060665</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>18.65928798531922</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.3374256644367731</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.06963801728022639</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>宜進</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>172.1553085539658</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>45.512055394927</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>19.99132615262341</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.8348609736415091</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0147298748087928</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>台榮</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>171.9042477952381</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>38.38382357076729</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>30.30191371637733</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.5942116369070093</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0183385446838285</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>年興</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>171.6909591493734</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>49.31627723615088</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>11.17032851585702</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.5584919651855531</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.0453369316386756</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>159.8703921308577</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>49.48317207004429</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>9.356195427416788</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>1.332329260188842</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>0.0149295173073751</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>濱川</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>153.992834816581</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>41.03348304742002</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>14.1495462379899</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.5156235209366679</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.0932497315529958</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>131.0032214725879</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>34.2869672304565</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>15.14909258404206</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.5409608012391172</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0.0231260323310376</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>大宇</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>81.55552797341271</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>31.57245759113273</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>14.86745737527452</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.7572572916786937</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.0119745482591869</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>1325</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>恆大</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D78" s="2" t="n">
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>81.2224697907068</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>26.1</v>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
         <v>43.9608806912912</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>12.8241025191739</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>0.6294322188050135</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="K133" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N78" s="2" t="n">
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>-0.0464958818346795</v>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
